--- a/output7/【河洛文讀注音-雅俗通】《心經》.xlsx
+++ b/output7/【河洛文讀注音-雅俗通】《心經》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F00B069-8C9C-4FDB-AD88-B3F5C1C64FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57383CCE-2041-4948-A667-A44E8A0EF046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" tabRatio="718" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -3041,7 +3041,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3212,26 +3212,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="2" borderId="3" xfId="5" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -5652,19 +5632,19 @@
     <row r="3" spans="1:22" s="12" customFormat="1" ht="60" customHeight="1">
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
-      <c r="D3" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="58" t="s">
+      <c r="D3" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="41" t="s">
         <v>42</v>
       </c>
       <c r="I3" s="41" t="s">
@@ -5707,19 +5687,19 @@
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="14"/>
-      <c r="D4" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="59" t="s">
+      <c r="D4" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="59" t="s">
+      <c r="G4" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="43" t="s">
         <v>42</v>
       </c>
       <c r="I4" s="43" t="s">
@@ -5761,19 +5741,19 @@
       <c r="B5" s="15">
         <v>1</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="57" t="s">
+      <c r="E5" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="57" t="str">
+      <c r="H5" s="44" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -5816,19 +5796,19 @@
     <row r="6" spans="1:22" s="18" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="16"/>
       <c r="C6" s="17"/>
-      <c r="D6" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="59" t="s">
+      <c r="D6" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="59" t="s">
+      <c r="G6" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="43" t="s">
         <v>42</v>
       </c>
       <c r="I6" s="43" t="s">
@@ -5869,49 +5849,49 @@
     <row r="7" spans="1:22" s="22" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="19"/>
       <c r="C7" s="20"/>
-      <c r="D7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R7" s="58" t="s">
+      <c r="D7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q7" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R7" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S7" s="50" t="s">
@@ -5921,52 +5901,52 @@
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="14"/>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="E8" s="59" t="s">
+      <c r="E8" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="G8" s="59" t="s">
+      <c r="G8" s="43" t="s">
         <v>418</v>
       </c>
-      <c r="H8" s="59" t="s">
+      <c r="H8" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="I8" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="59" t="s">
+      <c r="I8" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="59" t="s">
+      <c r="K8" s="43" t="s">
         <v>425</v>
       </c>
-      <c r="L8" s="59" t="s">
+      <c r="L8" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="M8" s="59" t="s">
+      <c r="M8" s="43" t="s">
         <v>431</v>
       </c>
-      <c r="N8" s="59" t="s">
+      <c r="N8" s="43" t="s">
         <v>434</v>
       </c>
-      <c r="O8" s="59" t="s">
+      <c r="O8" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="P8" s="59" t="s">
+      <c r="P8" s="43" t="s">
         <v>440</v>
       </c>
-      <c r="Q8" s="59" t="s">
+      <c r="Q8" s="43" t="s">
         <v>443</v>
       </c>
-      <c r="R8" s="59" t="s">
+      <c r="R8" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="S8" s="61" t="s">
+      <c r="S8" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V8" s="55"/>
@@ -5976,52 +5956,52 @@
         <f>B5+1</f>
         <v>2</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="G9" s="57" t="s">
+      <c r="G9" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="H9" s="57" t="s">
+      <c r="H9" s="44" t="s">
         <v>225</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="J9" s="57" t="s">
+      <c r="J9" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="K9" s="57" t="s">
+      <c r="K9" s="44" t="s">
         <v>228</v>
       </c>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="M9" s="57" t="s">
+      <c r="M9" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="N9" s="57" t="s">
+      <c r="N9" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="O9" s="57" t="s">
+      <c r="O9" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="P9" s="57" t="s">
+      <c r="P9" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="Q9" s="57" t="s">
+      <c r="Q9" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="R9" s="57" t="s">
+      <c r="R9" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="S9" s="60" t="s">
+      <c r="S9" s="47" t="s">
         <v>42</v>
       </c>
       <c r="T9" s="13"/>
@@ -6029,52 +6009,52 @@
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="16"/>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="E10" s="59" t="s">
+      <c r="E10" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="43" t="s">
         <v>419</v>
       </c>
-      <c r="H10" s="59" t="s">
+      <c r="H10" s="43" t="s">
         <v>422</v>
       </c>
-      <c r="I10" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="59" t="s">
+      <c r="I10" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="K10" s="59" t="s">
+      <c r="K10" s="43" t="s">
         <v>426</v>
       </c>
-      <c r="L10" s="59" t="s">
+      <c r="L10" s="43" t="s">
         <v>429</v>
       </c>
-      <c r="M10" s="59" t="s">
+      <c r="M10" s="43" t="s">
         <v>432</v>
       </c>
-      <c r="N10" s="59" t="s">
+      <c r="N10" s="43" t="s">
         <v>435</v>
       </c>
-      <c r="O10" s="59" t="s">
+      <c r="O10" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="P10" s="59" t="s">
+      <c r="P10" s="43" t="s">
         <v>441</v>
       </c>
-      <c r="Q10" s="59" t="s">
+      <c r="Q10" s="43" t="s">
         <v>444</v>
       </c>
-      <c r="R10" s="59" t="s">
+      <c r="R10" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="S10" s="62" t="s">
+      <c r="S10" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V10" s="55"/>
@@ -6082,49 +6062,49 @@
     <row r="11" spans="1:22" s="21" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
-      <c r="D11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q11" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R11" s="58" t="s">
+      <c r="D11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q11" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R11" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S11" s="50" t="s">
@@ -6134,49 +6114,49 @@
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="14"/>
-      <c r="D12" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="59" t="s">
+      <c r="D12" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="43" t="s">
         <v>205</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="43" t="s">
         <v>448</v>
       </c>
-      <c r="G12" s="59" t="s">
+      <c r="G12" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="H12" s="59" t="s">
+      <c r="H12" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="I12" s="59" t="s">
+      <c r="I12" s="43" t="s">
         <v>455</v>
       </c>
-      <c r="J12" s="59" t="s">
+      <c r="J12" s="43" t="s">
         <v>458</v>
       </c>
-      <c r="K12" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L12" s="59" t="s">
+      <c r="K12" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L12" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="M12" s="59" t="s">
+      <c r="M12" s="43" t="s">
         <v>462</v>
       </c>
-      <c r="N12" s="59" t="s">
+      <c r="N12" s="43" t="s">
         <v>465</v>
       </c>
-      <c r="O12" s="59" t="s">
+      <c r="O12" s="43" t="s">
         <v>468</v>
       </c>
-      <c r="P12" s="59" t="s">
+      <c r="P12" s="43" t="s">
         <v>471</v>
       </c>
-      <c r="Q12" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R12" s="59" t="s">
+      <c r="Q12" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R12" s="43" t="s">
         <v>42</v>
       </c>
       <c r="S12" s="46" t="s">
@@ -6189,49 +6169,49 @@
         <f>B9+1</f>
         <v>3</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="D13" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="F13" s="57" t="s">
+      <c r="F13" s="44" t="s">
         <v>242</v>
       </c>
-      <c r="G13" s="57" t="s">
+      <c r="G13" s="44" t="s">
         <v>244</v>
       </c>
-      <c r="H13" s="57" t="s">
+      <c r="H13" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="J13" s="57" t="s">
+      <c r="J13" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="K13" s="57" t="s">
+      <c r="K13" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="L13" s="57" t="s">
+      <c r="L13" s="44" t="s">
         <v>252</v>
       </c>
-      <c r="M13" s="57" t="s">
+      <c r="M13" s="44" t="s">
         <v>254</v>
       </c>
-      <c r="N13" s="57" t="s">
+      <c r="N13" s="44" t="s">
         <v>256</v>
       </c>
-      <c r="O13" s="57" t="s">
+      <c r="O13" s="44" t="s">
         <v>258</v>
       </c>
-      <c r="P13" s="57" t="s">
+      <c r="P13" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="Q13" s="57" t="s">
+      <c r="Q13" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="R13" s="57" t="str">
+      <c r="R13" s="44" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -6243,49 +6223,49 @@
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="16"/>
-      <c r="D14" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="59" t="s">
+      <c r="D14" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="43" t="s">
         <v>449</v>
       </c>
-      <c r="G14" s="59" t="s">
+      <c r="G14" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="H14" s="59" t="s">
+      <c r="H14" s="43" t="s">
         <v>453</v>
       </c>
-      <c r="I14" s="59" t="s">
+      <c r="I14" s="43" t="s">
         <v>456</v>
       </c>
-      <c r="J14" s="59" t="s">
+      <c r="J14" s="43" t="s">
         <v>459</v>
       </c>
-      <c r="K14" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L14" s="59" t="s">
+      <c r="K14" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="M14" s="59" t="s">
+      <c r="M14" s="43" t="s">
         <v>463</v>
       </c>
-      <c r="N14" s="59" t="s">
+      <c r="N14" s="43" t="s">
         <v>466</v>
       </c>
-      <c r="O14" s="59" t="s">
+      <c r="O14" s="43" t="s">
         <v>469</v>
       </c>
-      <c r="P14" s="59" t="s">
+      <c r="P14" s="43" t="s">
         <v>472</v>
       </c>
-      <c r="Q14" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R14" s="59" t="s">
+      <c r="Q14" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R14" s="43" t="s">
         <v>42</v>
       </c>
       <c r="S14" s="49" t="s">
@@ -6296,49 +6276,49 @@
     <row r="15" spans="1:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="10"/>
       <c r="C15" s="25"/>
-      <c r="D15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q15" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R15" s="58" t="s">
+      <c r="D15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R15" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S15" s="51" t="s">
@@ -6348,52 +6328,52 @@
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="14"/>
-      <c r="D16" s="59" t="s">
+      <c r="D16" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="43" t="s">
         <v>479</v>
       </c>
-      <c r="G16" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="59" t="s">
+      <c r="G16" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="I16" s="59" t="s">
+      <c r="I16" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="59" t="s">
+      <c r="J16" s="43" t="s">
         <v>482</v>
       </c>
-      <c r="K16" s="59" t="s">
+      <c r="K16" s="43" t="s">
         <v>458</v>
       </c>
-      <c r="L16" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M16" s="59" t="s">
+      <c r="L16" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M16" s="43" t="s">
         <v>458</v>
       </c>
-      <c r="N16" s="59" t="s">
+      <c r="N16" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="O16" s="59" t="s">
+      <c r="O16" s="43" t="s">
         <v>482</v>
       </c>
-      <c r="P16" s="59" t="s">
+      <c r="P16" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="Q16" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R16" s="59" t="s">
+      <c r="Q16" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R16" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="S16" s="61" t="s">
+      <c r="S16" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V16" s="55"/>
@@ -6403,104 +6383,104 @@
         <f>B13+1</f>
         <v>4</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="E17" s="57" t="s">
+      <c r="E17" s="44" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="57" t="s">
+      <c r="F17" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="57" t="s">
+      <c r="G17" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="57" t="s">
+      <c r="H17" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="I17" s="57" t="s">
+      <c r="I17" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="57" t="s">
+      <c r="J17" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="K17" s="57" t="s">
+      <c r="K17" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="L17" s="57" t="s">
+      <c r="L17" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="M17" s="57" t="s">
+      <c r="M17" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="N17" s="57" t="s">
+      <c r="N17" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="O17" s="57" t="s">
+      <c r="O17" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="P17" s="57" t="s">
+      <c r="P17" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="Q17" s="57" t="s">
+      <c r="Q17" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="R17" s="57" t="s">
+      <c r="R17" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="S17" s="60" t="s">
+      <c r="S17" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V17" s="55"/>
     </row>
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="16"/>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="43" t="s">
         <v>477</v>
       </c>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="43" t="s">
         <v>480</v>
       </c>
-      <c r="G18" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="59" t="s">
+      <c r="G18" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="I18" s="59" t="s">
+      <c r="I18" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="59" t="s">
+      <c r="J18" s="43" t="s">
         <v>483</v>
       </c>
-      <c r="K18" s="59" t="s">
+      <c r="K18" s="43" t="s">
         <v>459</v>
       </c>
-      <c r="L18" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M18" s="59" t="s">
+      <c r="L18" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" s="43" t="s">
         <v>459</v>
       </c>
-      <c r="N18" s="59" t="s">
+      <c r="N18" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="O18" s="59" t="s">
+      <c r="O18" s="43" t="s">
         <v>483</v>
       </c>
-      <c r="P18" s="59" t="s">
+      <c r="P18" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="Q18" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R18" s="59" t="s">
+      <c r="Q18" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R18" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="S18" s="62" t="s">
+      <c r="S18" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V18" s="55"/>
@@ -6508,49 +6488,49 @@
     <row r="19" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="10"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q19" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R19" s="58" t="s">
+      <c r="D19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q19" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R19" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S19" s="51" t="s">
@@ -6560,52 +6540,52 @@
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="14"/>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="43" t="s">
         <v>486</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="43" t="s">
         <v>458</v>
       </c>
-      <c r="G20" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="59" t="s">
+      <c r="G20" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="43" t="s">
         <v>458</v>
       </c>
-      <c r="I20" s="59" t="s">
+      <c r="I20" s="43" t="s">
         <v>486</v>
       </c>
-      <c r="J20" s="59" t="s">
+      <c r="J20" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="K20" s="59" t="s">
+      <c r="K20" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="L20" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M20" s="59" t="s">
+      <c r="L20" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M20" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="N20" s="59" t="s">
+      <c r="N20" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="O20" s="59" t="s">
+      <c r="O20" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="P20" s="59" t="s">
+      <c r="P20" s="43" t="s">
         <v>490</v>
       </c>
-      <c r="Q20" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R20" s="59" t="s">
+      <c r="Q20" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R20" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="S20" s="61" t="s">
+      <c r="S20" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V20" s="55"/>
@@ -6615,104 +6595,104 @@
         <f>B17+1</f>
         <v>5</v>
       </c>
-      <c r="D21" s="57" t="s">
+      <c r="D21" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="E21" s="57" t="s">
+      <c r="E21" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="57" t="s">
+      <c r="F21" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="G21" s="57" t="s">
+      <c r="G21" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="H21" s="57" t="s">
+      <c r="H21" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="I21" s="57" t="s">
+      <c r="I21" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="J21" s="57" t="s">
+      <c r="J21" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="K21" s="57" t="s">
+      <c r="K21" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="L21" s="57" t="s">
+      <c r="L21" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="M21" s="57" t="s">
+      <c r="M21" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="N21" s="57" t="s">
+      <c r="N21" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="O21" s="57" t="s">
+      <c r="O21" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="P21" s="57" t="s">
+      <c r="P21" s="44" t="s">
         <v>277</v>
       </c>
-      <c r="Q21" s="57" t="s">
+      <c r="Q21" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="R21" s="57" t="s">
+      <c r="R21" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="S21" s="60" t="s">
+      <c r="S21" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V21" s="55"/>
     </row>
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="16"/>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="43" t="s">
         <v>487</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="43" t="s">
         <v>459</v>
       </c>
-      <c r="G22" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="59" t="s">
+      <c r="G22" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="43" t="s">
         <v>459</v>
       </c>
-      <c r="I22" s="59" t="s">
+      <c r="I22" s="43" t="s">
         <v>487</v>
       </c>
-      <c r="J22" s="59" t="s">
+      <c r="J22" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="K22" s="59" t="s">
+      <c r="K22" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="L22" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M22" s="59" t="s">
+      <c r="L22" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M22" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="N22" s="59" t="s">
+      <c r="N22" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="O22" s="59" t="s">
+      <c r="O22" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="P22" s="59" t="s">
+      <c r="P22" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="Q22" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R22" s="59" t="s">
+      <c r="Q22" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R22" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="S22" s="62" t="s">
+      <c r="S22" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V22" s="55"/>
@@ -6720,19 +6700,19 @@
     <row r="23" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="10"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="58" t="s">
+      <c r="D23" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" s="41" t="s">
         <v>42</v>
       </c>
       <c r="I23" s="41" t="s">
@@ -6772,19 +6752,19 @@
     </row>
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="14"/>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="43" t="s">
         <v>493</v>
       </c>
-      <c r="E24" s="59" t="s">
+      <c r="E24" s="43" t="s">
         <v>496</v>
       </c>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="G24" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="59" t="s">
+      <c r="G24" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="43" t="s">
         <v>42</v>
       </c>
       <c r="I24" s="43" t="s">
@@ -6827,19 +6807,19 @@
         <f>B21+1</f>
         <v>6</v>
       </c>
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="44" t="s">
         <v>280</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="44" t="s">
         <v>282</v>
       </c>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="G25" s="57" t="s">
+      <c r="G25" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="57" t="str">
+      <c r="H25" s="44" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -6881,19 +6861,19 @@
     </row>
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="16"/>
-      <c r="D26" s="59" t="s">
+      <c r="D26" s="43" t="s">
         <v>494</v>
       </c>
-      <c r="E26" s="59" t="s">
+      <c r="E26" s="43" t="s">
         <v>497</v>
       </c>
-      <c r="F26" s="59" t="s">
+      <c r="F26" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="G26" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H26" s="59" t="s">
+      <c r="G26" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="43" t="s">
         <v>42</v>
       </c>
       <c r="I26" s="43" t="s">
@@ -6934,49 +6914,49 @@
     <row r="27" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B27" s="10"/>
       <c r="C27" s="25"/>
-      <c r="D27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q27" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R27" s="58" t="s">
+      <c r="D27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R27" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S27" s="51" t="s">
@@ -6986,52 +6966,52 @@
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="14"/>
-      <c r="D28" s="59" t="s">
+      <c r="D28" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="E28" s="59" t="s">
+      <c r="E28" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="43" t="s">
         <v>479</v>
       </c>
-      <c r="G28" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H28" s="59" t="s">
+      <c r="G28" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="I28" s="59" t="s">
+      <c r="I28" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="J28" s="59" t="s">
+      <c r="J28" s="43" t="s">
         <v>499</v>
       </c>
-      <c r="K28" s="59" t="s">
+      <c r="K28" s="43" t="s">
         <v>458</v>
       </c>
-      <c r="L28" s="59" t="s">
+      <c r="L28" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="M28" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="N28" s="59" t="s">
+      <c r="M28" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="N28" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="O28" s="59" t="s">
+      <c r="O28" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="P28" s="59" t="s">
+      <c r="P28" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="Q28" s="59" t="s">
+      <c r="Q28" s="43" t="s">
         <v>504</v>
       </c>
-      <c r="R28" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S28" s="61" t="s">
+      <c r="R28" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="S28" s="46" t="s">
         <v>42</v>
       </c>
       <c r="U28" s="26"/>
@@ -7042,52 +7022,52 @@
         <f>B25+1</f>
         <v>7</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="44" t="s">
         <v>264</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="G29" s="57" t="s">
+      <c r="G29" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="H29" s="57" t="s">
+      <c r="H29" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="I29" s="57" t="s">
+      <c r="I29" s="44" t="s">
         <v>284</v>
       </c>
-      <c r="J29" s="57" t="s">
+      <c r="J29" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="K29" s="57" t="s">
+      <c r="K29" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="L29" s="57" t="s">
+      <c r="L29" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="M29" s="57" t="s">
+      <c r="M29" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="N29" s="57" t="s">
+      <c r="N29" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="O29" s="57" t="s">
+      <c r="O29" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="P29" s="57" t="s">
+      <c r="P29" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="Q29" s="57" t="s">
+      <c r="Q29" s="44" t="s">
         <v>290</v>
       </c>
-      <c r="R29" s="57" t="s">
+      <c r="R29" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="S29" s="60" t="s">
+      <c r="S29" s="47" t="s">
         <v>42</v>
       </c>
       <c r="U29" s="26"/>
@@ -7095,52 +7075,52 @@
     </row>
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="16"/>
-      <c r="D30" s="59" t="s">
+      <c r="D30" s="43" t="s">
         <v>477</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="43" t="s">
         <v>480</v>
       </c>
-      <c r="G30" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H30" s="59" t="s">
+      <c r="G30" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="I30" s="59" t="s">
+      <c r="I30" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="J30" s="59" t="s">
+      <c r="J30" s="43" t="s">
         <v>500</v>
       </c>
-      <c r="K30" s="59" t="s">
+      <c r="K30" s="43" t="s">
         <v>459</v>
       </c>
-      <c r="L30" s="59" t="s">
+      <c r="L30" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="M30" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="N30" s="59" t="s">
+      <c r="M30" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="N30" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="O30" s="59" t="s">
+      <c r="O30" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="P30" s="59" t="s">
+      <c r="P30" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="Q30" s="59" t="s">
+      <c r="Q30" s="43" t="s">
         <v>505</v>
       </c>
-      <c r="R30" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S30" s="62" t="s">
+      <c r="R30" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="S30" s="49" t="s">
         <v>42</v>
       </c>
       <c r="U30" s="26"/>
@@ -7149,49 +7129,49 @@
     <row r="31" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B31" s="10"/>
       <c r="C31" s="25"/>
-      <c r="D31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q31" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R31" s="58" t="s">
+      <c r="D31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q31" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R31" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S31" s="51" t="s">
@@ -7201,52 +7181,52 @@
     </row>
     <row r="32" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="14"/>
-      <c r="D32" s="59" t="s">
+      <c r="D32" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="59" t="s">
+      <c r="E32" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="F32" s="59" t="s">
+      <c r="F32" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="G32" s="59" t="s">
+      <c r="G32" s="43" t="s">
         <v>511</v>
       </c>
-      <c r="H32" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32" s="59" t="s">
+      <c r="H32" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="I32" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="J32" s="59" t="s">
+      <c r="J32" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="K32" s="59" t="s">
+      <c r="K32" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="L32" s="59" t="s">
+      <c r="L32" s="43" t="s">
         <v>515</v>
       </c>
-      <c r="M32" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="N32" s="59" t="s">
+      <c r="M32" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="N32" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="O32" s="59" t="s">
+      <c r="O32" s="43" t="s">
         <v>518</v>
       </c>
-      <c r="P32" s="59" t="s">
+      <c r="P32" s="43" t="s">
         <v>458</v>
       </c>
-      <c r="Q32" s="59" t="s">
+      <c r="Q32" s="43" t="s">
         <v>521</v>
       </c>
-      <c r="R32" s="59" t="s">
+      <c r="R32" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="S32" s="61" t="s">
+      <c r="S32" s="46" t="s">
         <v>42</v>
       </c>
       <c r="U32" s="26"/>
@@ -7257,104 +7237,104 @@
         <f>B29+1</f>
         <v>8</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="57" t="s">
+      <c r="E33" s="44" t="s">
         <v>292</v>
       </c>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="57" t="s">
+      <c r="G33" s="44" t="s">
         <v>294</v>
       </c>
-      <c r="H33" s="57" t="s">
+      <c r="H33" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="I33" s="57" t="s">
+      <c r="I33" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="J33" s="57" t="s">
+      <c r="J33" s="44" t="s">
         <v>296</v>
       </c>
-      <c r="K33" s="57" t="s">
+      <c r="K33" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="57" t="s">
+      <c r="L33" s="44" t="s">
         <v>298</v>
       </c>
-      <c r="M33" s="57" t="s">
+      <c r="M33" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="N33" s="57" t="s">
+      <c r="N33" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="O33" s="57" t="s">
+      <c r="O33" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="P33" s="57" t="s">
+      <c r="P33" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="Q33" s="57" t="s">
+      <c r="Q33" s="44" t="s">
         <v>302</v>
       </c>
-      <c r="R33" s="57" t="s">
+      <c r="R33" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="S33" s="60" t="s">
+      <c r="S33" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V33" s="55"/>
     </row>
     <row r="34" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="16"/>
-      <c r="D34" s="59" t="s">
+      <c r="D34" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="E34" s="59" t="s">
+      <c r="E34" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="F34" s="59" t="s">
+      <c r="F34" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="G34" s="59" t="s">
+      <c r="G34" s="43" t="s">
         <v>512</v>
       </c>
-      <c r="H34" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="I34" s="59" t="s">
+      <c r="H34" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="I34" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="J34" s="59" t="s">
+      <c r="J34" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="K34" s="59" t="s">
+      <c r="K34" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="L34" s="59" t="s">
+      <c r="L34" s="43" t="s">
         <v>516</v>
       </c>
-      <c r="M34" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="N34" s="59" t="s">
+      <c r="M34" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="N34" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="O34" s="59" t="s">
+      <c r="O34" s="43" t="s">
         <v>519</v>
       </c>
-      <c r="P34" s="59" t="s">
+      <c r="P34" s="43" t="s">
         <v>459</v>
       </c>
-      <c r="Q34" s="59" t="s">
+      <c r="Q34" s="43" t="s">
         <v>522</v>
       </c>
-      <c r="R34" s="59" t="s">
+      <c r="R34" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="S34" s="62" t="s">
+      <c r="S34" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V34" s="55"/>
@@ -7362,49 +7342,49 @@
     <row r="35" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B35" s="10"/>
       <c r="C35" s="25"/>
-      <c r="D35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q35" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R35" s="58" t="s">
+      <c r="D35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R35" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S35" s="51" t="s">
@@ -7414,52 +7394,52 @@
     </row>
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="14"/>
-      <c r="D36" s="59" t="s">
+      <c r="D36" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="59" t="s">
+      <c r="E36" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="59" t="s">
+      <c r="G36" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="H36" s="59" t="s">
+      <c r="H36" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="I36" s="59" t="s">
+      <c r="I36" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="J36" s="59" t="s">
+      <c r="J36" s="43" t="s">
         <v>490</v>
       </c>
-      <c r="K36" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L36" s="59" t="s">
+      <c r="K36" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L36" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="M36" s="59" t="s">
+      <c r="M36" s="43" t="s">
         <v>527</v>
       </c>
-      <c r="N36" s="59" t="s">
+      <c r="N36" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="O36" s="59" t="s">
+      <c r="O36" s="43" t="s">
         <v>530</v>
       </c>
-      <c r="P36" s="59" t="s">
+      <c r="P36" s="43" t="s">
         <v>533</v>
       </c>
-      <c r="Q36" s="59" t="s">
+      <c r="Q36" s="43" t="s">
         <v>536</v>
       </c>
-      <c r="R36" s="59" t="s">
+      <c r="R36" s="43" t="s">
         <v>539</v>
       </c>
-      <c r="S36" s="61" t="s">
+      <c r="S36" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V36" s="55"/>
@@ -7469,104 +7449,104 @@
         <f>B33+1</f>
         <v>9</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="E37" s="57" t="s">
+      <c r="E37" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="G37" s="57" t="s">
+      <c r="G37" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="H37" s="57" t="s">
+      <c r="H37" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="I37" s="57" t="s">
+      <c r="I37" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="J37" s="57" t="s">
+      <c r="J37" s="44" t="s">
         <v>277</v>
       </c>
-      <c r="K37" s="57" t="s">
+      <c r="K37" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="L37" s="57" t="s">
+      <c r="L37" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="M37" s="57" t="s">
+      <c r="M37" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="N37" s="57" t="s">
+      <c r="N37" s="44" t="s">
         <v>306</v>
       </c>
-      <c r="O37" s="57" t="s">
+      <c r="O37" s="44" t="s">
         <v>308</v>
       </c>
-      <c r="P37" s="57" t="s">
+      <c r="P37" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="Q37" s="57" t="s">
+      <c r="Q37" s="44" t="s">
         <v>312</v>
       </c>
-      <c r="R37" s="57" t="s">
+      <c r="R37" s="44" t="s">
         <v>314</v>
       </c>
-      <c r="S37" s="60" t="s">
+      <c r="S37" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V37" s="55"/>
     </row>
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="16"/>
-      <c r="D38" s="59" t="s">
+      <c r="D38" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="E38" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="59" t="s">
+      <c r="E38" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="G38" s="59" t="s">
+      <c r="G38" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="H38" s="59" t="s">
+      <c r="H38" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="I38" s="59" t="s">
+      <c r="I38" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="J38" s="59" t="s">
+      <c r="J38" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="K38" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L38" s="59" t="s">
+      <c r="K38" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L38" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="M38" s="59" t="s">
+      <c r="M38" s="43" t="s">
         <v>528</v>
       </c>
-      <c r="N38" s="59" t="s">
+      <c r="N38" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="O38" s="59" t="s">
+      <c r="O38" s="43" t="s">
         <v>531</v>
       </c>
-      <c r="P38" s="59" t="s">
+      <c r="P38" s="43" t="s">
         <v>534</v>
       </c>
-      <c r="Q38" s="59" t="s">
+      <c r="Q38" s="43" t="s">
         <v>537</v>
       </c>
-      <c r="R38" s="59" t="s">
+      <c r="R38" s="43" t="s">
         <v>540</v>
       </c>
-      <c r="S38" s="62" t="s">
+      <c r="S38" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V38" s="55"/>
@@ -7574,34 +7554,34 @@
     <row r="39" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B39" s="10"/>
       <c r="C39" s="25"/>
-      <c r="D39" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E39" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F39" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G39" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H39" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I39" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J39" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K39" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L39" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M39" s="58" t="s">
+      <c r="D39" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H39" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J39" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K39" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L39" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M39" s="41" t="s">
         <v>42</v>
       </c>
       <c r="N39" s="41" t="s">
@@ -7626,34 +7606,34 @@
     </row>
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="14"/>
-      <c r="D40" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="E40" s="59" t="s">
+      <c r="D40" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E40" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="F40" s="59" t="s">
+      <c r="F40" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="G40" s="59" t="s">
+      <c r="G40" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="H40" s="59" t="s">
+      <c r="H40" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="I40" s="59" t="s">
+      <c r="I40" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="J40" s="59" t="s">
+      <c r="J40" s="43" t="s">
         <v>548</v>
       </c>
-      <c r="K40" s="59" t="s">
+      <c r="K40" s="43" t="s">
         <v>499</v>
       </c>
-      <c r="L40" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M40" s="59" t="s">
+      <c r="L40" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M40" s="43" t="s">
         <v>42</v>
       </c>
       <c r="N40" s="43" t="s">
@@ -7681,34 +7661,34 @@
         <f>B37+1</f>
         <v>10</v>
       </c>
-      <c r="D41" s="57" t="s">
+      <c r="D41" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="E41" s="57" t="s">
+      <c r="E41" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F41" s="57" t="s">
+      <c r="F41" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="G41" s="57" t="s">
+      <c r="G41" s="44" t="s">
         <v>316</v>
       </c>
-      <c r="H41" s="57" t="s">
+      <c r="H41" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="I41" s="57" t="s">
+      <c r="I41" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="J41" s="57" t="s">
+      <c r="J41" s="44" t="s">
         <v>322</v>
       </c>
-      <c r="K41" s="57" t="s">
+      <c r="K41" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="L41" s="57" t="s">
+      <c r="L41" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="M41" s="57" t="str">
+      <c r="M41" s="44" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -7735,34 +7715,34 @@
     </row>
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="16"/>
-      <c r="D42" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="E42" s="59" t="s">
+      <c r="D42" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E42" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="F42" s="59" t="s">
+      <c r="F42" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="G42" s="59" t="s">
+      <c r="G42" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="H42" s="59" t="s">
+      <c r="H42" s="43" t="s">
         <v>155</v>
       </c>
-      <c r="I42" s="59" t="s">
+      <c r="I42" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="J42" s="59" t="s">
+      <c r="J42" s="43" t="s">
         <v>549</v>
       </c>
-      <c r="K42" s="59" t="s">
+      <c r="K42" s="43" t="s">
         <v>500</v>
       </c>
-      <c r="L42" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M42" s="59" t="s">
+      <c r="L42" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M42" s="43" t="s">
         <v>42</v>
       </c>
       <c r="N42" s="43" t="s">
@@ -7788,49 +7768,49 @@
     <row r="43" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B43" s="10"/>
       <c r="C43" s="25"/>
-      <c r="D43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q43" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R43" s="58" t="s">
+      <c r="D43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q43" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R43" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S43" s="51" t="s">
@@ -7840,52 +7820,52 @@
     </row>
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="14"/>
-      <c r="D44" s="59" t="s">
+      <c r="D44" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="43" t="s">
         <v>527</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="43" t="s">
         <v>556</v>
       </c>
-      <c r="G44" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H44" s="59" t="s">
+      <c r="G44" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H44" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="I44" s="59" t="s">
+      <c r="I44" s="43" t="s">
         <v>560</v>
       </c>
-      <c r="J44" s="59" t="s">
+      <c r="J44" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="K44" s="59" t="s">
+      <c r="K44" s="43" t="s">
         <v>539</v>
       </c>
-      <c r="L44" s="59" t="s">
+      <c r="L44" s="43" t="s">
         <v>490</v>
       </c>
-      <c r="M44" s="59" t="s">
+      <c r="M44" s="43" t="s">
         <v>556</v>
       </c>
-      <c r="N44" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="O44" s="59" t="s">
+      <c r="N44" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="O44" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="P44" s="59" t="s">
+      <c r="P44" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="Q44" s="59" t="s">
+      <c r="Q44" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="R44" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S44" s="61" t="s">
+      <c r="R44" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="S44" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V44" s="55"/>
@@ -7895,104 +7875,104 @@
         <f>B41+1</f>
         <v>11</v>
       </c>
-      <c r="D45" s="57" t="s">
+      <c r="D45" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="E45" s="57" t="s">
+      <c r="E45" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="F45" s="57" t="s">
+      <c r="F45" s="44" t="s">
         <v>324</v>
       </c>
-      <c r="G45" s="57" t="s">
+      <c r="G45" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="H45" s="57" t="s">
+      <c r="H45" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="I45" s="57" t="s">
+      <c r="I45" s="44" t="s">
         <v>327</v>
       </c>
-      <c r="J45" s="57" t="s">
+      <c r="J45" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="K45" s="57" t="s">
+      <c r="K45" s="44" t="s">
         <v>314</v>
       </c>
-      <c r="L45" s="57" t="s">
+      <c r="L45" s="44" t="s">
         <v>277</v>
       </c>
-      <c r="M45" s="57" t="s">
+      <c r="M45" s="44" t="s">
         <v>324</v>
       </c>
-      <c r="N45" s="57" t="s">
+      <c r="N45" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="O45" s="57" t="s">
+      <c r="O45" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="P45" s="57" t="s">
+      <c r="P45" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="Q45" s="57" t="s">
+      <c r="Q45" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="R45" s="57" t="s">
+      <c r="R45" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="S45" s="60" t="s">
+      <c r="S45" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V45" s="55"/>
     </row>
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="16"/>
-      <c r="D46" s="59" t="s">
+      <c r="D46" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="E46" s="59" t="s">
+      <c r="E46" s="43" t="s">
         <v>528</v>
       </c>
-      <c r="F46" s="59" t="s">
+      <c r="F46" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="G46" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H46" s="59" t="s">
+      <c r="G46" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H46" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="I46" s="59" t="s">
+      <c r="I46" s="43" t="s">
         <v>561</v>
       </c>
-      <c r="J46" s="59" t="s">
+      <c r="J46" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="K46" s="59" t="s">
+      <c r="K46" s="43" t="s">
         <v>540</v>
       </c>
-      <c r="L46" s="59" t="s">
+      <c r="L46" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="M46" s="59" t="s">
+      <c r="M46" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="N46" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="O46" s="59" t="s">
+      <c r="N46" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="O46" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="P46" s="59" t="s">
+      <c r="P46" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="Q46" s="59" t="s">
+      <c r="Q46" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="R46" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S46" s="62" t="s">
+      <c r="R46" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="S46" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V46" s="55"/>
@@ -8000,49 +7980,49 @@
     <row r="47" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B47" s="10"/>
       <c r="C47" s="25"/>
-      <c r="D47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q47" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R47" s="58" t="s">
+      <c r="D47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q47" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R47" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S47" s="51" t="s">
@@ -8052,52 +8032,52 @@
     </row>
     <row r="48" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="14"/>
-      <c r="D48" s="59" t="s">
+      <c r="D48" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="59" t="s">
+      <c r="E48" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="F48" s="59" t="s">
+      <c r="F48" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="G48" s="59" t="s">
+      <c r="G48" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="H48" s="59" t="s">
+      <c r="H48" s="43" t="s">
         <v>567</v>
       </c>
-      <c r="I48" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J48" s="59" t="s">
+      <c r="I48" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J48" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="K48" s="59" t="s">
+      <c r="K48" s="43" t="s">
         <v>560</v>
       </c>
-      <c r="L48" s="59" t="s">
+      <c r="L48" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="M48" s="59" t="s">
+      <c r="M48" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="N48" s="59" t="s">
+      <c r="N48" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="O48" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="P48" s="59" t="s">
+      <c r="O48" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="P48" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="Q48" s="59" t="s">
+      <c r="Q48" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="R48" s="59" t="s">
+      <c r="R48" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="S48" s="61" t="s">
+      <c r="S48" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V48" s="55"/>
@@ -8107,104 +8087,104 @@
         <f>B45+1</f>
         <v>12</v>
       </c>
-      <c r="D49" s="57" t="s">
+      <c r="D49" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="E49" s="57" t="s">
+      <c r="E49" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F49" s="57" t="s">
+      <c r="F49" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="G49" s="57" t="s">
+      <c r="G49" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="H49" s="57" t="s">
+      <c r="H49" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="I49" s="57" t="s">
+      <c r="I49" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="J49" s="57" t="s">
+      <c r="J49" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="K49" s="57" t="s">
+      <c r="K49" s="44" t="s">
         <v>327</v>
       </c>
-      <c r="L49" s="57" t="s">
+      <c r="L49" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="M49" s="57" t="s">
+      <c r="M49" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="N49" s="57" t="s">
+      <c r="N49" s="44" t="s">
         <v>331</v>
       </c>
-      <c r="O49" s="57" t="s">
+      <c r="O49" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="P49" s="57" t="s">
+      <c r="P49" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="Q49" s="57" t="s">
+      <c r="Q49" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="R49" s="57" t="s">
+      <c r="R49" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="S49" s="60" t="s">
+      <c r="S49" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V49" s="55"/>
     </row>
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="16"/>
-      <c r="D50" s="59" t="s">
+      <c r="D50" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="E50" s="59" t="s">
+      <c r="E50" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="F50" s="59" t="s">
+      <c r="F50" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="G50" s="59" t="s">
+      <c r="G50" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="H50" s="59" t="s">
+      <c r="H50" s="43" t="s">
         <v>568</v>
       </c>
-      <c r="I50" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J50" s="59" t="s">
+      <c r="I50" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J50" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="K50" s="59" t="s">
+      <c r="K50" s="43" t="s">
         <v>561</v>
       </c>
-      <c r="L50" s="59" t="s">
+      <c r="L50" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="M50" s="59" t="s">
+      <c r="M50" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="N50" s="59" t="s">
+      <c r="N50" s="43" t="s">
         <v>571</v>
       </c>
-      <c r="O50" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="P50" s="59" t="s">
+      <c r="O50" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="P50" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="Q50" s="59" t="s">
+      <c r="Q50" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="R50" s="59" t="s">
+      <c r="R50" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="S50" s="62" t="s">
+      <c r="S50" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V50" s="55"/>
@@ -8212,16 +8192,16 @@
     <row r="51" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B51" s="10"/>
       <c r="C51" s="25"/>
-      <c r="D51" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E51" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G51" s="58" t="s">
+      <c r="D51" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G51" s="41" t="s">
         <v>42</v>
       </c>
       <c r="H51" s="41" t="s">
@@ -8264,16 +8244,16 @@
     </row>
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="14"/>
-      <c r="D52" s="59" t="s">
+      <c r="D52" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="E52" s="59" t="s">
+      <c r="E52" s="43" t="s">
         <v>567</v>
       </c>
-      <c r="F52" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="G52" s="59" t="s">
+      <c r="F52" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" s="43" t="s">
         <v>42</v>
       </c>
       <c r="H52" s="43" t="s">
@@ -8319,16 +8299,16 @@
         <f>B49+1</f>
         <v>13</v>
       </c>
-      <c r="D53" s="57" t="s">
+      <c r="D53" s="44" t="s">
         <v>331</v>
       </c>
-      <c r="E53" s="57" t="s">
+      <c r="E53" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F53" s="57" t="s">
+      <c r="F53" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="G53" s="57" t="str">
+      <c r="G53" s="44" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -8373,16 +8353,16 @@
     </row>
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="16"/>
-      <c r="D54" s="59" t="s">
+      <c r="D54" s="43" t="s">
         <v>571</v>
       </c>
-      <c r="E54" s="59" t="s">
+      <c r="E54" s="43" t="s">
         <v>568</v>
       </c>
-      <c r="F54" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="G54" s="59" t="s">
+      <c r="F54" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54" s="43" t="s">
         <v>42</v>
       </c>
       <c r="H54" s="43" t="s">
@@ -8426,49 +8406,49 @@
     <row r="55" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B55" s="10"/>
       <c r="C55" s="25"/>
-      <c r="D55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q55" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R55" s="58" t="s">
+      <c r="D55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q55" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R55" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S55" s="51" t="s">
@@ -8478,52 +8458,52 @@
     </row>
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="14"/>
-      <c r="D56" s="59" t="s">
+      <c r="D56" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="E56" s="59" t="s">
+      <c r="E56" s="43" t="s">
         <v>468</v>
       </c>
-      <c r="F56" s="59" t="s">
+      <c r="F56" s="43" t="s">
         <v>578</v>
       </c>
-      <c r="G56" s="59" t="s">
+      <c r="G56" s="43" t="s">
         <v>504</v>
       </c>
-      <c r="H56" s="59" t="s">
+      <c r="H56" s="43" t="s">
         <v>581</v>
       </c>
-      <c r="I56" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J56" s="59" t="s">
+      <c r="I56" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J56" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="K56" s="59" t="s">
+      <c r="K56" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="L56" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M56" s="59" t="s">
+      <c r="L56" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M56" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="N56" s="59" t="s">
+      <c r="N56" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="O56" s="59" t="s">
+      <c r="O56" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="P56" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q56" s="59" t="s">
+      <c r="P56" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q56" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="R56" s="59" t="s">
+      <c r="R56" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="S56" s="61" t="s">
+      <c r="S56" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V56" s="55"/>
@@ -8533,104 +8513,104 @@
         <f>B53+1</f>
         <v>14</v>
       </c>
-      <c r="D57" s="57" t="s">
+      <c r="D57" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="E57" s="57" t="s">
+      <c r="E57" s="44" t="s">
         <v>258</v>
       </c>
-      <c r="F57" s="57" t="s">
+      <c r="F57" s="44" t="s">
         <v>333</v>
       </c>
-      <c r="G57" s="57" t="s">
+      <c r="G57" s="44" t="s">
         <v>290</v>
       </c>
-      <c r="H57" s="57" t="s">
+      <c r="H57" s="44" t="s">
         <v>335</v>
       </c>
-      <c r="I57" s="57" t="s">
+      <c r="I57" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="J57" s="57" t="s">
+      <c r="J57" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="K57" s="57" t="s">
+      <c r="K57" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="L57" s="57" t="s">
+      <c r="L57" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="M57" s="57" t="s">
+      <c r="M57" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="N57" s="57" t="s">
+      <c r="N57" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="O57" s="57" t="s">
+      <c r="O57" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="P57" s="57" t="s">
+      <c r="P57" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="Q57" s="57" t="s">
+      <c r="Q57" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="R57" s="57" t="s">
+      <c r="R57" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="S57" s="60" t="s">
+      <c r="S57" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V57" s="55"/>
     </row>
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="16"/>
-      <c r="D58" s="59" t="s">
+      <c r="D58" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="43" t="s">
         <v>469</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="43" t="s">
         <v>579</v>
       </c>
-      <c r="G58" s="59" t="s">
+      <c r="G58" s="43" t="s">
         <v>505</v>
       </c>
-      <c r="H58" s="59" t="s">
+      <c r="H58" s="43" t="s">
         <v>582</v>
       </c>
-      <c r="I58" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J58" s="59" t="s">
+      <c r="I58" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J58" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="K58" s="59" t="s">
+      <c r="K58" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="L58" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M58" s="59" t="s">
+      <c r="L58" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M58" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="N58" s="59" t="s">
+      <c r="N58" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="O58" s="59" t="s">
+      <c r="O58" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="P58" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q58" s="59" t="s">
+      <c r="P58" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q58" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="R58" s="59" t="s">
+      <c r="R58" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="S58" s="62" t="s">
+      <c r="S58" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V58" s="55"/>
@@ -8638,49 +8618,49 @@
     <row r="59" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B59" s="10"/>
       <c r="C59" s="25"/>
-      <c r="D59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R59" s="58" t="s">
+      <c r="D59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R59" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S59" s="51" t="s">
@@ -8690,52 +8670,52 @@
     </row>
     <row r="60" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="14"/>
-      <c r="D60" s="59" t="s">
+      <c r="D60" s="43" t="s">
         <v>593</v>
       </c>
-      <c r="E60" s="59" t="s">
+      <c r="E60" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="F60" s="59" t="s">
+      <c r="F60" s="43" t="s">
         <v>518</v>
       </c>
-      <c r="G60" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H60" s="59" t="s">
+      <c r="G60" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" s="43" t="s">
         <v>418</v>
       </c>
-      <c r="I60" s="59" t="s">
+      <c r="I60" s="43" t="s">
         <v>596</v>
       </c>
-      <c r="J60" s="59" t="s">
+      <c r="J60" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="K60" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L60" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M60" s="59" t="s">
+      <c r="K60" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L60" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M60" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="N60" s="59" t="s">
+      <c r="N60" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="O60" s="59" t="s">
+      <c r="O60" s="43" t="s">
         <v>431</v>
       </c>
-      <c r="P60" s="59" t="s">
+      <c r="P60" s="43" t="s">
         <v>434</v>
       </c>
-      <c r="Q60" s="59" t="s">
+      <c r="Q60" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="R60" s="59" t="s">
+      <c r="R60" s="43" t="s">
         <v>440</v>
       </c>
-      <c r="S60" s="61" t="s">
+      <c r="S60" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V60" s="55"/>
@@ -8745,104 +8725,104 @@
         <f>B57+1</f>
         <v>15</v>
       </c>
-      <c r="D61" s="57" t="s">
+      <c r="D61" s="44" t="s">
         <v>341</v>
       </c>
-      <c r="E61" s="57" t="s">
+      <c r="E61" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F61" s="57" t="s">
+      <c r="F61" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="G61" s="57" t="s">
+      <c r="G61" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="H61" s="57" t="s">
+      <c r="H61" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="I61" s="57" t="s">
+      <c r="I61" s="44" t="s">
         <v>343</v>
       </c>
-      <c r="J61" s="57" t="s">
+      <c r="J61" s="44" t="s">
         <v>225</v>
       </c>
-      <c r="K61" s="57" t="s">
+      <c r="K61" s="44" t="s">
         <v>345</v>
       </c>
-      <c r="L61" s="57" t="s">
+      <c r="L61" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="M61" s="57" t="s">
+      <c r="M61" s="44" t="s">
         <v>347</v>
       </c>
-      <c r="N61" s="57" t="s">
+      <c r="N61" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="O61" s="57" t="s">
+      <c r="O61" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="P61" s="57" t="s">
+      <c r="P61" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="Q61" s="57" t="s">
+      <c r="Q61" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="R61" s="57" t="s">
+      <c r="R61" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="S61" s="60" t="s">
+      <c r="S61" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V61" s="55"/>
     </row>
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="16"/>
-      <c r="D62" s="59" t="s">
+      <c r="D62" s="43" t="s">
         <v>594</v>
       </c>
-      <c r="E62" s="59" t="s">
+      <c r="E62" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="F62" s="59" t="s">
+      <c r="F62" s="43" t="s">
         <v>519</v>
       </c>
-      <c r="G62" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H62" s="59" t="s">
+      <c r="G62" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H62" s="43" t="s">
         <v>419</v>
       </c>
-      <c r="I62" s="59" t="s">
+      <c r="I62" s="43" t="s">
         <v>597</v>
       </c>
-      <c r="J62" s="59" t="s">
+      <c r="J62" s="43" t="s">
         <v>422</v>
       </c>
-      <c r="K62" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L62" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M62" s="59" t="s">
+      <c r="K62" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L62" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M62" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="N62" s="59" t="s">
+      <c r="N62" s="43" t="s">
         <v>429</v>
       </c>
-      <c r="O62" s="59" t="s">
+      <c r="O62" s="43" t="s">
         <v>432</v>
       </c>
-      <c r="P62" s="59" t="s">
+      <c r="P62" s="43" t="s">
         <v>435</v>
       </c>
-      <c r="Q62" s="59" t="s">
+      <c r="Q62" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="R62" s="59" t="s">
+      <c r="R62" s="43" t="s">
         <v>441</v>
       </c>
-      <c r="S62" s="62" t="s">
+      <c r="S62" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V62" s="55"/>
@@ -8850,49 +8830,49 @@
     <row r="63" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B63" s="10"/>
       <c r="C63" s="25"/>
-      <c r="D63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q63" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R63" s="58" t="s">
+      <c r="D63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q63" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R63" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S63" s="51" t="s">
@@ -8902,52 +8882,52 @@
     </row>
     <row r="64" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B64" s="14"/>
-      <c r="D64" s="59" t="s">
+      <c r="D64" s="43" t="s">
         <v>443</v>
       </c>
-      <c r="E64" s="59" t="s">
+      <c r="E64" s="43" t="s">
         <v>518</v>
       </c>
-      <c r="F64" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="G64" s="59" t="s">
+      <c r="F64" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="H64" s="59" t="s">
+      <c r="H64" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="I64" s="59" t="s">
+      <c r="I64" s="43" t="s">
         <v>602</v>
       </c>
-      <c r="J64" s="59" t="s">
+      <c r="J64" s="43" t="s">
         <v>605</v>
       </c>
-      <c r="K64" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L64" s="59" t="s">
+      <c r="K64" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L64" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="M64" s="59" t="s">
+      <c r="M64" s="43" t="s">
         <v>602</v>
       </c>
-      <c r="N64" s="59" t="s">
+      <c r="N64" s="43" t="s">
         <v>605</v>
       </c>
-      <c r="O64" s="59" t="s">
+      <c r="O64" s="43" t="s">
         <v>518</v>
       </c>
-      <c r="P64" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q64" s="59" t="s">
+      <c r="P64" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q64" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="R64" s="59" t="s">
+      <c r="R64" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="S64" s="61" t="s">
+      <c r="S64" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V64" s="55"/>
@@ -8957,104 +8937,104 @@
         <f>B61+1</f>
         <v>16</v>
       </c>
-      <c r="D65" s="57" t="s">
+      <c r="D65" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="F65" s="57" t="s">
+      <c r="F65" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="G65" s="57" t="s">
+      <c r="G65" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="I65" s="57" t="s">
+      <c r="I65" s="44" t="s">
         <v>349</v>
       </c>
-      <c r="J65" s="57" t="s">
+      <c r="J65" s="44" t="s">
         <v>351</v>
       </c>
-      <c r="K65" s="57" t="s">
+      <c r="K65" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="L65" s="57" t="s">
+      <c r="L65" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="M65" s="57" t="s">
+      <c r="M65" s="44" t="s">
         <v>349</v>
       </c>
-      <c r="N65" s="57" t="s">
+      <c r="N65" s="44" t="s">
         <v>351</v>
       </c>
-      <c r="O65" s="57" t="s">
+      <c r="O65" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="P65" s="57" t="s">
+      <c r="P65" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="Q65" s="57" t="s">
+      <c r="Q65" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="R65" s="57" t="s">
+      <c r="R65" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="S65" s="60" t="s">
+      <c r="S65" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V65" s="55"/>
     </row>
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="16"/>
-      <c r="D66" s="59" t="s">
+      <c r="D66" s="43" t="s">
         <v>444</v>
       </c>
-      <c r="E66" s="59" t="s">
+      <c r="E66" s="43" t="s">
         <v>519</v>
       </c>
-      <c r="F66" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="G66" s="59" t="s">
+      <c r="F66" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="H66" s="59" t="s">
+      <c r="H66" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="I66" s="59" t="s">
+      <c r="I66" s="43" t="s">
         <v>603</v>
       </c>
-      <c r="J66" s="59" t="s">
+      <c r="J66" s="43" t="s">
         <v>606</v>
       </c>
-      <c r="K66" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L66" s="59" t="s">
+      <c r="K66" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L66" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="M66" s="59" t="s">
+      <c r="M66" s="43" t="s">
         <v>603</v>
       </c>
-      <c r="N66" s="59" t="s">
+      <c r="N66" s="43" t="s">
         <v>606</v>
       </c>
-      <c r="O66" s="59" t="s">
+      <c r="O66" s="43" t="s">
         <v>519</v>
       </c>
-      <c r="P66" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q66" s="59" t="s">
+      <c r="P66" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q66" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="R66" s="59" t="s">
+      <c r="R66" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="S66" s="62" t="s">
+      <c r="S66" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V66" s="55"/>
@@ -9062,49 +9042,49 @@
     <row r="67" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B67" s="10"/>
       <c r="C67" s="25"/>
-      <c r="D67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q67" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R67" s="58" t="s">
+      <c r="D67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q67" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R67" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S67" s="51" t="s">
@@ -9114,52 +9094,52 @@
     </row>
     <row r="68" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="14"/>
-      <c r="D68" s="59" t="s">
+      <c r="D68" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="E68" s="59" t="s">
+      <c r="E68" s="43" t="s">
         <v>612</v>
       </c>
-      <c r="F68" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="G68" s="59" t="s">
+      <c r="F68" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="H68" s="59" t="s">
+      <c r="H68" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="I68" s="59" t="s">
+      <c r="I68" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="J68" s="59" t="s">
+      <c r="J68" s="43" t="s">
         <v>618</v>
       </c>
-      <c r="K68" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L68" s="59" t="s">
+      <c r="K68" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L68" s="43" t="s">
         <v>621</v>
       </c>
-      <c r="M68" s="59" t="s">
+      <c r="M68" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="N68" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="O68" s="59" t="s">
+      <c r="N68" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="O68" s="43" t="s">
         <v>624</v>
       </c>
-      <c r="P68" s="59" t="s">
+      <c r="P68" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="Q68" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R68" s="59" t="s">
+      <c r="Q68" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R68" s="43" t="s">
         <v>628</v>
       </c>
-      <c r="S68" s="61" t="s">
+      <c r="S68" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V68" s="55"/>
@@ -9169,104 +9149,104 @@
         <f>B65+1</f>
         <v>17</v>
       </c>
-      <c r="D69" s="57" t="s">
+      <c r="D69" s="44" t="s">
         <v>352</v>
       </c>
-      <c r="E69" s="57" t="s">
+      <c r="E69" s="44" t="s">
         <v>354</v>
       </c>
-      <c r="F69" s="57" t="s">
+      <c r="F69" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="G69" s="57" t="s">
+      <c r="G69" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="H69" s="57" t="s">
+      <c r="H69" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="I69" s="57" t="s">
+      <c r="I69" s="44" t="s">
         <v>357</v>
       </c>
-      <c r="J69" s="57" t="s">
+      <c r="J69" s="44" t="s">
         <v>359</v>
       </c>
-      <c r="K69" s="57" t="s">
+      <c r="K69" s="44" t="s">
         <v>360</v>
       </c>
-      <c r="L69" s="57" t="s">
+      <c r="L69" s="44" t="s">
         <v>362</v>
       </c>
-      <c r="M69" s="57" t="s">
+      <c r="M69" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="N69" s="57" t="s">
+      <c r="N69" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="O69" s="57" t="s">
+      <c r="O69" s="44" t="s">
         <v>364</v>
       </c>
-      <c r="P69" s="57" t="s">
+      <c r="P69" s="44" t="s">
         <v>366</v>
       </c>
-      <c r="Q69" s="57" t="s">
+      <c r="Q69" s="44" t="s">
         <v>368</v>
       </c>
-      <c r="R69" s="57" t="s">
+      <c r="R69" s="44" t="s">
         <v>370</v>
       </c>
-      <c r="S69" s="60" t="s">
+      <c r="S69" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V69" s="55"/>
     </row>
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="16"/>
-      <c r="D70" s="59" t="s">
+      <c r="D70" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="E70" s="59" t="s">
+      <c r="E70" s="43" t="s">
         <v>613</v>
       </c>
-      <c r="F70" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="G70" s="59" t="s">
+      <c r="F70" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="H70" s="59" t="s">
+      <c r="H70" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="I70" s="59" t="s">
+      <c r="I70" s="43" t="s">
         <v>616</v>
       </c>
-      <c r="J70" s="59" t="s">
+      <c r="J70" s="43" t="s">
         <v>619</v>
       </c>
-      <c r="K70" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L70" s="59" t="s">
+      <c r="K70" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L70" s="43" t="s">
         <v>622</v>
       </c>
-      <c r="M70" s="59" t="s">
+      <c r="M70" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="N70" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="O70" s="59" t="s">
+      <c r="N70" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="O70" s="43" t="s">
         <v>625</v>
       </c>
-      <c r="P70" s="59" t="s">
+      <c r="P70" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="Q70" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R70" s="59" t="s">
+      <c r="Q70" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R70" s="43" t="s">
         <v>629</v>
       </c>
-      <c r="S70" s="62" t="s">
+      <c r="S70" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V70" s="55"/>
@@ -9274,10 +9254,10 @@
     <row r="71" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B71" s="10"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E71" s="58" t="s">
+      <c r="D71" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E71" s="41" t="s">
         <v>42</v>
       </c>
       <c r="F71" s="41" t="s">
@@ -9326,10 +9306,10 @@
     </row>
     <row r="72" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="14"/>
-      <c r="D72" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="E72" s="59" t="s">
+      <c r="D72" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E72" s="43" t="s">
         <v>42</v>
       </c>
       <c r="F72" s="43" t="s">
@@ -9381,10 +9361,10 @@
         <f>B69+1</f>
         <v>18</v>
       </c>
-      <c r="D73" s="57" t="s">
+      <c r="D73" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="E73" s="57" t="str">
+      <c r="E73" s="44" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -9435,10 +9415,10 @@
     </row>
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="16"/>
-      <c r="D74" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="E74" s="59" t="s">
+      <c r="D74" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E74" s="43" t="s">
         <v>42</v>
       </c>
       <c r="F74" s="43" t="s">
@@ -9488,49 +9468,49 @@
     <row r="75" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B75" s="10"/>
       <c r="C75" s="25"/>
-      <c r="D75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q75" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R75" s="58" t="s">
+      <c r="D75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q75" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R75" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S75" s="51" t="s">
@@ -9540,52 +9520,52 @@
     </row>
     <row r="76" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="14"/>
-      <c r="D76" s="59" t="s">
+      <c r="D76" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="E76" s="59" t="s">
+      <c r="E76" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="F76" s="59" t="s">
+      <c r="F76" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="G76" s="59" t="s">
+      <c r="G76" s="43" t="s">
         <v>645</v>
       </c>
-      <c r="H76" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="I76" s="59" t="s">
+      <c r="H76" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="I76" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="J76" s="59" t="s">
+      <c r="J76" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="K76" s="59" t="s">
+      <c r="K76" s="43" t="s">
         <v>431</v>
       </c>
-      <c r="L76" s="59" t="s">
+      <c r="L76" s="43" t="s">
         <v>434</v>
       </c>
-      <c r="M76" s="59" t="s">
+      <c r="M76" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="N76" s="59" t="s">
+      <c r="N76" s="43" t="s">
         <v>440</v>
       </c>
-      <c r="O76" s="59" t="s">
+      <c r="O76" s="43" t="s">
         <v>443</v>
       </c>
-      <c r="P76" s="59" t="s">
+      <c r="P76" s="43" t="s">
         <v>518</v>
       </c>
-      <c r="Q76" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R76" s="59" t="s">
+      <c r="Q76" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R76" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="S76" s="61" t="s">
+      <c r="S76" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V76" s="55"/>
@@ -9595,104 +9575,104 @@
         <f>B73+1</f>
         <v>19</v>
       </c>
-      <c r="D77" s="57" t="s">
+      <c r="D77" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="E77" s="57" t="s">
+      <c r="E77" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="F77" s="57" t="s">
+      <c r="F77" s="44" t="s">
         <v>284</v>
       </c>
-      <c r="G77" s="57" t="s">
+      <c r="G77" s="44" t="s">
         <v>374</v>
       </c>
-      <c r="H77" s="57" t="s">
+      <c r="H77" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="I77" s="57" t="s">
+      <c r="I77" s="44" t="s">
         <v>347</v>
       </c>
-      <c r="J77" s="57" t="s">
+      <c r="J77" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="K77" s="57" t="s">
+      <c r="K77" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="L77" s="57" t="s">
+      <c r="L77" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="M77" s="57" t="s">
+      <c r="M77" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="N77" s="57" t="s">
+      <c r="N77" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="O77" s="57" t="s">
+      <c r="O77" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="P77" s="57" t="s">
+      <c r="P77" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="Q77" s="57" t="s">
+      <c r="Q77" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="R77" s="57" t="s">
+      <c r="R77" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="S77" s="60" t="s">
+      <c r="S77" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V77" s="55"/>
     </row>
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="16"/>
-      <c r="D78" s="59" t="s">
+      <c r="D78" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="E78" s="59" t="s">
+      <c r="E78" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="F78" s="59" t="s">
+      <c r="F78" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="G78" s="59" t="s">
+      <c r="G78" s="43" t="s">
         <v>646</v>
       </c>
-      <c r="H78" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="I78" s="59" t="s">
+      <c r="H78" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="I78" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="J78" s="59" t="s">
+      <c r="J78" s="43" t="s">
         <v>429</v>
       </c>
-      <c r="K78" s="59" t="s">
+      <c r="K78" s="43" t="s">
         <v>432</v>
       </c>
-      <c r="L78" s="59" t="s">
+      <c r="L78" s="43" t="s">
         <v>435</v>
       </c>
-      <c r="M78" s="59" t="s">
+      <c r="M78" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="N78" s="59" t="s">
+      <c r="N78" s="43" t="s">
         <v>441</v>
       </c>
-      <c r="O78" s="59" t="s">
+      <c r="O78" s="43" t="s">
         <v>444</v>
       </c>
-      <c r="P78" s="59" t="s">
+      <c r="P78" s="43" t="s">
         <v>519</v>
       </c>
-      <c r="Q78" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R78" s="59" t="s">
+      <c r="Q78" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R78" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="S78" s="62" t="s">
+      <c r="S78" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V78" s="55"/>
@@ -9700,37 +9680,37 @@
     <row r="79" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B79" s="10"/>
       <c r="C79" s="25"/>
-      <c r="D79" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E79" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F79" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G79" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H79" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I79" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J79" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K79" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L79" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M79" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N79" s="58" t="s">
+      <c r="D79" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E79" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H79" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J79" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K79" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L79" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M79" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N79" s="41" t="s">
         <v>42</v>
       </c>
       <c r="O79" s="41" t="s">
@@ -9752,37 +9732,37 @@
     </row>
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="14"/>
-      <c r="D80" s="59" t="s">
+      <c r="D80" s="43" t="s">
         <v>653</v>
       </c>
-      <c r="E80" s="59" t="s">
+      <c r="E80" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="F80" s="59" t="s">
+      <c r="F80" s="43" t="s">
         <v>443</v>
       </c>
-      <c r="G80" s="59" t="s">
+      <c r="G80" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="H80" s="59" t="s">
+      <c r="H80" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="I80" s="59" t="s">
+      <c r="I80" s="43" t="s">
         <v>657</v>
       </c>
-      <c r="J80" s="59" t="s">
+      <c r="J80" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="K80" s="59" t="s">
+      <c r="K80" s="43" t="s">
         <v>418</v>
       </c>
-      <c r="L80" s="59" t="s">
+      <c r="L80" s="43" t="s">
         <v>596</v>
       </c>
-      <c r="M80" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="N80" s="59" t="s">
+      <c r="M80" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="N80" s="43" t="s">
         <v>42</v>
       </c>
       <c r="O80" s="43" t="s">
@@ -9807,37 +9787,37 @@
         <f>B77+1</f>
         <v>20</v>
       </c>
-      <c r="D81" s="57" t="s">
+      <c r="D81" s="44" t="s">
         <v>376</v>
       </c>
-      <c r="E81" s="57" t="s">
+      <c r="E81" s="44" t="s">
         <v>378</v>
       </c>
-      <c r="F81" s="57" t="s">
+      <c r="F81" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="G81" s="57" t="s">
+      <c r="G81" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="H81" s="57" t="s">
+      <c r="H81" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="I81" s="57" t="s">
+      <c r="I81" s="44" t="s">
         <v>380</v>
       </c>
-      <c r="J81" s="57" t="s">
+      <c r="J81" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="K81" s="57" t="s">
+      <c r="K81" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="L81" s="57" t="s">
+      <c r="L81" s="44" t="s">
         <v>343</v>
       </c>
-      <c r="M81" s="57" t="s">
+      <c r="M81" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="N81" s="57" t="str">
+      <c r="N81" s="44" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -9861,37 +9841,37 @@
     </row>
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="16"/>
-      <c r="D82" s="59" t="s">
+      <c r="D82" s="43" t="s">
         <v>654</v>
       </c>
-      <c r="E82" s="59" t="s">
+      <c r="E82" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="F82" s="59" t="s">
+      <c r="F82" s="43" t="s">
         <v>444</v>
       </c>
-      <c r="G82" s="59" t="s">
+      <c r="G82" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="H82" s="59" t="s">
+      <c r="H82" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="I82" s="59" t="s">
+      <c r="I82" s="43" t="s">
         <v>658</v>
       </c>
-      <c r="J82" s="59" t="s">
+      <c r="J82" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="K82" s="59" t="s">
+      <c r="K82" s="43" t="s">
         <v>419</v>
       </c>
-      <c r="L82" s="59" t="s">
+      <c r="L82" s="43" t="s">
         <v>597</v>
       </c>
-      <c r="M82" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="N82" s="59" t="s">
+      <c r="M82" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="N82" s="43" t="s">
         <v>42</v>
       </c>
       <c r="O82" s="43" t="s">
@@ -9914,49 +9894,49 @@
     <row r="83" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B83" s="10"/>
       <c r="C83" s="25"/>
-      <c r="D83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q83" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R83" s="58" t="s">
+      <c r="D83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q83" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R83" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S83" s="51" t="s">
@@ -9966,52 +9946,52 @@
     </row>
     <row r="84" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B84" s="14"/>
-      <c r="D84" s="59" t="s">
+      <c r="D84" s="43" t="s">
         <v>518</v>
       </c>
-      <c r="E84" s="59" t="s">
+      <c r="E84" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="F84" s="59" t="s">
+      <c r="F84" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="G84" s="59" t="s">
+      <c r="G84" s="43" t="s">
         <v>431</v>
       </c>
-      <c r="H84" s="59" t="s">
+      <c r="H84" s="43" t="s">
         <v>434</v>
       </c>
-      <c r="I84" s="59" t="s">
+      <c r="I84" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="J84" s="59" t="s">
+      <c r="J84" s="43" t="s">
         <v>440</v>
       </c>
-      <c r="K84" s="59" t="s">
+      <c r="K84" s="43" t="s">
         <v>443</v>
       </c>
-      <c r="L84" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M84" s="59" t="s">
+      <c r="L84" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M84" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="N84" s="59" t="s">
+      <c r="N84" s="43" t="s">
         <v>664</v>
       </c>
-      <c r="O84" s="59" t="s">
+      <c r="O84" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="P84" s="59" t="s">
+      <c r="P84" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="Q84" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R84" s="59" t="s">
+      <c r="Q84" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R84" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="S84" s="61" t="s">
+      <c r="S84" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V84" s="7"/>
@@ -10021,104 +10001,104 @@
         <f>B81+1</f>
         <v>21</v>
       </c>
-      <c r="D85" s="57" t="s">
+      <c r="D85" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="E85" s="57" t="s">
+      <c r="E85" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="F85" s="57" t="s">
+      <c r="F85" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="G85" s="57" t="s">
+      <c r="G85" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="H85" s="57" t="s">
+      <c r="H85" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="I85" s="57" t="s">
+      <c r="I85" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="J85" s="57" t="s">
+      <c r="J85" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="K85" s="57" t="s">
+      <c r="K85" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="L85" s="57" t="s">
+      <c r="L85" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="M85" s="57" t="s">
+      <c r="M85" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="N85" s="57" t="s">
+      <c r="N85" s="44" t="s">
         <v>382</v>
       </c>
-      <c r="O85" s="57" t="s">
+      <c r="O85" s="44" t="s">
         <v>384</v>
       </c>
-      <c r="P85" s="57" t="s">
+      <c r="P85" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="Q85" s="57" t="s">
+      <c r="Q85" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="R85" s="57" t="s">
+      <c r="R85" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="S85" s="60" t="s">
+      <c r="S85" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V85" s="7"/>
     </row>
     <row r="86" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B86" s="16"/>
-      <c r="D86" s="59" t="s">
+      <c r="D86" s="43" t="s">
         <v>519</v>
       </c>
-      <c r="E86" s="59" t="s">
+      <c r="E86" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="F86" s="59" t="s">
+      <c r="F86" s="43" t="s">
         <v>429</v>
       </c>
-      <c r="G86" s="59" t="s">
+      <c r="G86" s="43" t="s">
         <v>432</v>
       </c>
-      <c r="H86" s="59" t="s">
+      <c r="H86" s="43" t="s">
         <v>435</v>
       </c>
-      <c r="I86" s="59" t="s">
+      <c r="I86" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="J86" s="59" t="s">
+      <c r="J86" s="43" t="s">
         <v>441</v>
       </c>
-      <c r="K86" s="59" t="s">
+      <c r="K86" s="43" t="s">
         <v>444</v>
       </c>
-      <c r="L86" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M86" s="59" t="s">
+      <c r="L86" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M86" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="N86" s="59" t="s">
+      <c r="N86" s="43" t="s">
         <v>665</v>
       </c>
-      <c r="O86" s="59" t="s">
+      <c r="O86" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="P86" s="59" t="s">
+      <c r="P86" s="43" t="s">
         <v>668</v>
       </c>
-      <c r="Q86" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="R86" s="59" t="s">
+      <c r="Q86" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="R86" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="S86" s="62" t="s">
+      <c r="S86" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V86" s="7"/>
@@ -10126,49 +10106,49 @@
     <row r="87" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B87" s="10"/>
       <c r="C87" s="25"/>
-      <c r="D87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q87" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R87" s="58" t="s">
+      <c r="D87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q87" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R87" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S87" s="51" t="s">
@@ -10178,52 +10158,52 @@
     </row>
     <row r="88" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B88" s="14"/>
-      <c r="D88" s="59" t="s">
+      <c r="D88" s="43" t="s">
         <v>664</v>
       </c>
-      <c r="E88" s="59" t="s">
+      <c r="E88" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="F88" s="59" t="s">
+      <c r="F88" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="G88" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H88" s="59" t="s">
+      <c r="G88" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H88" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="I88" s="59" t="s">
+      <c r="I88" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="J88" s="59" t="s">
+      <c r="J88" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="K88" s="59" t="s">
+      <c r="K88" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="L88" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M88" s="59" t="s">
+      <c r="L88" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M88" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="N88" s="59" t="s">
+      <c r="N88" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="O88" s="59" t="s">
+      <c r="O88" s="43" t="s">
         <v>672</v>
       </c>
-      <c r="P88" s="59" t="s">
+      <c r="P88" s="43" t="s">
         <v>672</v>
       </c>
-      <c r="Q88" s="59" t="s">
+      <c r="Q88" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="R88" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S88" s="61" t="s">
+      <c r="R88" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="S88" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V88" s="7"/>
@@ -10233,104 +10213,104 @@
         <f>B85+1</f>
         <v>22</v>
       </c>
-      <c r="D89" s="57" t="s">
+      <c r="D89" s="44" t="s">
         <v>382</v>
       </c>
-      <c r="E89" s="57" t="s">
+      <c r="E89" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="F89" s="57" t="s">
+      <c r="F89" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="G89" s="57" t="s">
+      <c r="G89" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="H89" s="57" t="s">
+      <c r="H89" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="I89" s="57" t="s">
+      <c r="I89" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="J89" s="57" t="s">
+      <c r="J89" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="K89" s="57" t="s">
+      <c r="K89" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="L89" s="57" t="s">
+      <c r="L89" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="M89" s="57" t="s">
+      <c r="M89" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="N89" s="57" t="s">
+      <c r="N89" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="O89" s="57" t="s">
+      <c r="O89" s="44" t="s">
         <v>388</v>
       </c>
-      <c r="P89" s="57" t="s">
+      <c r="P89" s="44" t="s">
         <v>388</v>
       </c>
-      <c r="Q89" s="57" t="s">
+      <c r="Q89" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="R89" s="57" t="s">
+      <c r="R89" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="S89" s="60" t="s">
+      <c r="S89" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V89" s="7"/>
     </row>
     <row r="90" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B90" s="16"/>
-      <c r="D90" s="59" t="s">
+      <c r="D90" s="43" t="s">
         <v>665</v>
       </c>
-      <c r="E90" s="59" t="s">
+      <c r="E90" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="F90" s="59" t="s">
+      <c r="F90" s="43" t="s">
         <v>668</v>
       </c>
-      <c r="G90" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="H90" s="59" t="s">
+      <c r="G90" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H90" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="I90" s="59" t="s">
+      <c r="I90" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="J90" s="59" t="s">
+      <c r="J90" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="K90" s="59" t="s">
+      <c r="K90" s="43" t="s">
         <v>668</v>
       </c>
-      <c r="L90" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="M90" s="59" t="s">
+      <c r="L90" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="M90" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="N90" s="59" t="s">
+      <c r="N90" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="O90" s="59" t="s">
+      <c r="O90" s="43" t="s">
         <v>673</v>
       </c>
-      <c r="P90" s="59" t="s">
+      <c r="P90" s="43" t="s">
         <v>673</v>
       </c>
-      <c r="Q90" s="59" t="s">
+      <c r="Q90" s="43" t="s">
         <v>668</v>
       </c>
-      <c r="R90" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S90" s="62" t="s">
+      <c r="R90" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="S90" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V90" s="7"/>
@@ -10338,40 +10318,40 @@
     <row r="91" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B91" s="10"/>
       <c r="C91" s="25"/>
-      <c r="D91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N91" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O91" s="58" t="s">
+      <c r="D91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N91" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O91" s="41" t="s">
         <v>42</v>
       </c>
       <c r="P91" s="41" t="s">
@@ -10390,40 +10370,40 @@
     </row>
     <row r="92" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B92" s="14"/>
-      <c r="D92" s="59" t="s">
+      <c r="D92" s="43" t="s">
         <v>681</v>
       </c>
-      <c r="E92" s="59" t="s">
+      <c r="E92" s="43" t="s">
         <v>684</v>
       </c>
-      <c r="F92" s="59" t="s">
+      <c r="F92" s="43" t="s">
         <v>462</v>
       </c>
-      <c r="G92" s="59" t="s">
+      <c r="G92" s="43" t="s">
         <v>465</v>
       </c>
-      <c r="H92" s="59" t="s">
+      <c r="H92" s="43" t="s">
         <v>468</v>
       </c>
-      <c r="I92" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J92" s="59" t="s">
+      <c r="I92" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J92" s="43" t="s">
         <v>687</v>
       </c>
-      <c r="K92" s="59" t="s">
+      <c r="K92" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="L92" s="59" t="s">
+      <c r="L92" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="M92" s="59" t="s">
+      <c r="M92" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="N92" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="O92" s="59" t="s">
+      <c r="N92" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="O92" s="43" t="s">
         <v>42</v>
       </c>
       <c r="P92" s="43" t="s">
@@ -10445,40 +10425,40 @@
         <f>B89+1</f>
         <v>23</v>
       </c>
-      <c r="D93" s="57" t="s">
+      <c r="D93" s="44" t="s">
         <v>390</v>
       </c>
-      <c r="E93" s="57" t="s">
+      <c r="E93" s="44" t="s">
         <v>392</v>
       </c>
-      <c r="F93" s="57" t="s">
+      <c r="F93" s="44" t="s">
         <v>254</v>
       </c>
-      <c r="G93" s="57" t="s">
+      <c r="G93" s="44" t="s">
         <v>256</v>
       </c>
-      <c r="H93" s="57" t="s">
+      <c r="H93" s="44" t="s">
         <v>258</v>
       </c>
-      <c r="I93" s="57" t="s">
+      <c r="I93" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="J93" s="57" t="s">
+      <c r="J93" s="44" t="s">
         <v>394</v>
       </c>
-      <c r="K93" s="57" t="s">
+      <c r="K93" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="L93" s="57" t="s">
+      <c r="L93" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="M93" s="57" t="s">
+      <c r="M93" s="44" t="s">
         <v>397</v>
       </c>
-      <c r="N93" s="57" t="s">
+      <c r="N93" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="O93" s="57" t="str">
+      <c r="O93" s="44" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -10499,40 +10479,40 @@
     </row>
     <row r="94" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="16"/>
-      <c r="D94" s="59" t="s">
+      <c r="D94" s="43" t="s">
         <v>682</v>
       </c>
-      <c r="E94" s="59" t="s">
+      <c r="E94" s="43" t="s">
         <v>685</v>
       </c>
-      <c r="F94" s="59" t="s">
+      <c r="F94" s="43" t="s">
         <v>463</v>
       </c>
-      <c r="G94" s="59" t="s">
+      <c r="G94" s="43" t="s">
         <v>466</v>
       </c>
-      <c r="H94" s="59" t="s">
+      <c r="H94" s="43" t="s">
         <v>469</v>
       </c>
-      <c r="I94" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J94" s="59" t="s">
+      <c r="I94" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J94" s="43" t="s">
         <v>688</v>
       </c>
-      <c r="K94" s="59" t="s">
+      <c r="K94" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="L94" s="59" t="s">
+      <c r="L94" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="M94" s="59" t="s">
+      <c r="M94" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="N94" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="O94" s="59" t="s">
+      <c r="N94" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="O94" s="43" t="s">
         <v>42</v>
       </c>
       <c r="P94" s="43" t="s">
@@ -10552,49 +10532,49 @@
     <row r="95" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B95" s="10"/>
       <c r="C95" s="25"/>
-      <c r="D95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q95" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R95" s="58" t="s">
+      <c r="D95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q95" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R95" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S95" s="51" t="s">
@@ -10604,52 +10584,52 @@
     </row>
     <row r="96" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B96" s="14"/>
-      <c r="D96" s="59" t="s">
+      <c r="D96" s="43" t="s">
         <v>518</v>
       </c>
-      <c r="E96" s="59" t="s">
+      <c r="E96" s="43" t="s">
         <v>701</v>
       </c>
-      <c r="F96" s="59" t="s">
+      <c r="F96" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="G96" s="59" t="s">
+      <c r="G96" s="43" t="s">
         <v>431</v>
       </c>
-      <c r="H96" s="59" t="s">
+      <c r="H96" s="43" t="s">
         <v>434</v>
       </c>
-      <c r="I96" s="59" t="s">
+      <c r="I96" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="J96" s="59" t="s">
+      <c r="J96" s="43" t="s">
         <v>440</v>
       </c>
-      <c r="K96" s="59" t="s">
+      <c r="K96" s="43" t="s">
         <v>443</v>
       </c>
-      <c r="L96" s="59" t="s">
+      <c r="L96" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="M96" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="N96" s="59" t="s">
+      <c r="M96" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="N96" s="43" t="s">
         <v>486</v>
       </c>
-      <c r="O96" s="59" t="s">
+      <c r="O96" s="43" t="s">
         <v>701</v>
       </c>
-      <c r="P96" s="59" t="s">
+      <c r="P96" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="Q96" s="59" t="s">
+      <c r="Q96" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="R96" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S96" s="61" t="s">
+      <c r="R96" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="S96" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V96" s="7"/>
@@ -10659,104 +10639,104 @@
         <f>B93+1</f>
         <v>24</v>
       </c>
-      <c r="D97" s="57" t="s">
+      <c r="D97" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="E97" s="57" t="s">
+      <c r="E97" s="44" t="s">
         <v>399</v>
       </c>
-      <c r="F97" s="57" t="s">
+      <c r="F97" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="G97" s="57" t="s">
+      <c r="G97" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="H97" s="57" t="s">
+      <c r="H97" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="I97" s="57" t="s">
+      <c r="I97" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="J97" s="57" t="s">
+      <c r="J97" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="K97" s="57" t="s">
+      <c r="K97" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="L97" s="57" t="s">
+      <c r="L97" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="M97" s="57" t="s">
+      <c r="M97" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="N97" s="57" t="s">
+      <c r="N97" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="O97" s="57" t="s">
+      <c r="O97" s="44" t="s">
         <v>399</v>
       </c>
-      <c r="P97" s="57" t="s">
+      <c r="P97" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="Q97" s="57" t="s">
+      <c r="Q97" s="44" t="s">
         <v>401</v>
       </c>
-      <c r="R97" s="57" t="s">
+      <c r="R97" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="S97" s="60" t="s">
+      <c r="S97" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V97" s="7"/>
     </row>
     <row r="98" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="16"/>
-      <c r="D98" s="59" t="s">
+      <c r="D98" s="43" t="s">
         <v>519</v>
       </c>
-      <c r="E98" s="59" t="s">
+      <c r="E98" s="43" t="s">
         <v>702</v>
       </c>
-      <c r="F98" s="59" t="s">
+      <c r="F98" s="43" t="s">
         <v>429</v>
       </c>
-      <c r="G98" s="59" t="s">
+      <c r="G98" s="43" t="s">
         <v>432</v>
       </c>
-      <c r="H98" s="59" t="s">
+      <c r="H98" s="43" t="s">
         <v>435</v>
       </c>
-      <c r="I98" s="59" t="s">
+      <c r="I98" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="J98" s="59" t="s">
+      <c r="J98" s="43" t="s">
         <v>441</v>
       </c>
-      <c r="K98" s="59" t="s">
+      <c r="K98" s="43" t="s">
         <v>444</v>
       </c>
-      <c r="L98" s="59" t="s">
+      <c r="L98" s="43" t="s">
         <v>668</v>
       </c>
-      <c r="M98" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="N98" s="59" t="s">
+      <c r="M98" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="N98" s="43" t="s">
         <v>487</v>
       </c>
-      <c r="O98" s="59" t="s">
+      <c r="O98" s="43" t="s">
         <v>702</v>
       </c>
-      <c r="P98" s="59" t="s">
+      <c r="P98" s="43" t="s">
         <v>668</v>
       </c>
-      <c r="Q98" s="59" t="s">
+      <c r="Q98" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="R98" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S98" s="62" t="s">
+      <c r="R98" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="S98" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V98" s="7"/>
@@ -10764,49 +10744,49 @@
     <row r="99" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B99" s="10"/>
       <c r="C99" s="25"/>
-      <c r="D99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="M99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="N99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="O99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="P99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q99" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="R99" s="58" t="s">
+      <c r="D99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="O99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="P99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q99" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="R99" s="41" t="s">
         <v>42</v>
       </c>
       <c r="S99" s="51" t="s">
@@ -10816,52 +10796,52 @@
     </row>
     <row r="100" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B100" s="14"/>
-      <c r="D100" s="59" t="s">
+      <c r="D100" s="43" t="s">
         <v>714</v>
       </c>
-      <c r="E100" s="59" t="s">
+      <c r="E100" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="F100" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="G100" s="59" t="s">
+      <c r="F100" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G100" s="43" t="s">
         <v>714</v>
       </c>
-      <c r="H100" s="59" t="s">
+      <c r="H100" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="I100" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J100" s="59" t="s">
+      <c r="I100" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J100" s="43" t="s">
         <v>434</v>
       </c>
-      <c r="K100" s="59" t="s">
+      <c r="K100" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="L100" s="59" t="s">
+      <c r="L100" s="43" t="s">
         <v>714</v>
       </c>
-      <c r="M100" s="59" t="s">
+      <c r="M100" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="N100" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="O100" s="59" t="s">
+      <c r="N100" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="O100" s="43" t="s">
         <v>434</v>
       </c>
-      <c r="P100" s="59" t="s">
+      <c r="P100" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="Q100" s="59" t="s">
+      <c r="Q100" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="R100" s="59" t="s">
+      <c r="R100" s="43" t="s">
         <v>714</v>
       </c>
-      <c r="S100" s="61" t="s">
+      <c r="S100" s="46" t="s">
         <v>42</v>
       </c>
       <c r="V100" s="7"/>
@@ -10871,104 +10851,104 @@
         <f>B97+1</f>
         <v>25</v>
       </c>
-      <c r="D101" s="57" t="s">
+      <c r="D101" s="44" t="s">
         <v>403</v>
       </c>
-      <c r="E101" s="57" t="s">
+      <c r="E101" s="44" t="s">
         <v>405</v>
       </c>
-      <c r="F101" s="57" t="s">
+      <c r="F101" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="G101" s="57" t="s">
+      <c r="G101" s="44" t="s">
         <v>403</v>
       </c>
-      <c r="H101" s="57" t="s">
+      <c r="H101" s="44" t="s">
         <v>405</v>
       </c>
-      <c r="I101" s="57" t="s">
+      <c r="I101" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="J101" s="57" t="s">
+      <c r="J101" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="K101" s="57" t="s">
+      <c r="K101" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="L101" s="57" t="s">
+      <c r="L101" s="44" t="s">
         <v>403</v>
       </c>
-      <c r="M101" s="57" t="s">
+      <c r="M101" s="44" t="s">
         <v>405</v>
       </c>
-      <c r="N101" s="57" t="s">
+      <c r="N101" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="O101" s="57" t="s">
+      <c r="O101" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="P101" s="57" t="s">
+      <c r="P101" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="Q101" s="57" t="s">
+      <c r="Q101" s="44" t="s">
         <v>407</v>
       </c>
-      <c r="R101" s="57" t="s">
+      <c r="R101" s="44" t="s">
         <v>403</v>
       </c>
-      <c r="S101" s="60" t="s">
+      <c r="S101" s="47" t="s">
         <v>42</v>
       </c>
       <c r="V101" s="7"/>
     </row>
     <row r="102" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B102" s="16"/>
-      <c r="D102" s="59" t="s">
+      <c r="D102" s="43" t="s">
         <v>715</v>
       </c>
-      <c r="E102" s="59" t="s">
+      <c r="E102" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="F102" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="G102" s="59" t="s">
+      <c r="F102" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G102" s="43" t="s">
         <v>715</v>
       </c>
-      <c r="H102" s="59" t="s">
+      <c r="H102" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="I102" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J102" s="59" t="s">
+      <c r="I102" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J102" s="43" t="s">
         <v>435</v>
       </c>
-      <c r="K102" s="59" t="s">
+      <c r="K102" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="L102" s="59" t="s">
+      <c r="L102" s="43" t="s">
         <v>715</v>
       </c>
-      <c r="M102" s="59" t="s">
+      <c r="M102" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="N102" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="O102" s="59" t="s">
+      <c r="N102" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="O102" s="43" t="s">
         <v>435</v>
       </c>
-      <c r="P102" s="59" t="s">
+      <c r="P102" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="Q102" s="59" t="s">
+      <c r="Q102" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="R102" s="59" t="s">
+      <c r="R102" s="43" t="s">
         <v>715</v>
       </c>
-      <c r="S102" s="62" t="s">
+      <c r="S102" s="49" t="s">
         <v>42</v>
       </c>
       <c r="V102" s="7"/>
@@ -10976,31 +10956,31 @@
     <row r="103" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B103" s="10"/>
       <c r="C103" s="25"/>
-      <c r="D103" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="E103" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F103" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G103" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="H103" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="I103" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J103" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K103" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="L103" s="58" t="s">
+      <c r="D103" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E103" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F103" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G103" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H103" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="I103" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="J103" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K103" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L103" s="41" t="s">
         <v>42</v>
       </c>
       <c r="M103" s="41" t="s">
@@ -11028,31 +11008,31 @@
     </row>
     <row r="104" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B104" s="14"/>
-      <c r="D104" s="59" t="s">
+      <c r="D104" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="E104" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="F104" s="59" t="s">
+      <c r="E104" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="F104" s="43" t="s">
         <v>418</v>
       </c>
-      <c r="G104" s="59" t="s">
+      <c r="G104" s="43" t="s">
         <v>596</v>
       </c>
-      <c r="H104" s="59" t="s">
+      <c r="H104" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="I104" s="59" t="s">
+      <c r="I104" s="43" t="s">
         <v>722</v>
       </c>
-      <c r="J104" s="59" t="s">
+      <c r="J104" s="43" t="s">
         <v>725</v>
       </c>
-      <c r="K104" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L104" s="59" t="s">
+      <c r="K104" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L104" s="43" t="s">
         <v>42</v>
       </c>
       <c r="M104" s="43" t="s">
@@ -11083,31 +11063,31 @@
         <f>B101+1</f>
         <v>26</v>
       </c>
-      <c r="D105" s="57" t="s">
+      <c r="D105" s="44" t="s">
         <v>405</v>
       </c>
-      <c r="E105" s="57" t="s">
+      <c r="E105" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="F105" s="57" t="s">
+      <c r="F105" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="G105" s="57" t="s">
+      <c r="G105" s="44" t="s">
         <v>343</v>
       </c>
-      <c r="H105" s="57" t="s">
+      <c r="H105" s="44" t="s">
         <v>225</v>
       </c>
-      <c r="I105" s="57" t="s">
+      <c r="I105" s="44" t="s">
         <v>409</v>
       </c>
-      <c r="J105" s="57" t="s">
+      <c r="J105" s="44" t="s">
         <v>411</v>
       </c>
-      <c r="K105" s="57" t="s">
+      <c r="K105" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="L105" s="57" t="str">
+      <c r="L105" s="44" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -11137,31 +11117,31 @@
     </row>
     <row r="106" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B106" s="16"/>
-      <c r="D106" s="59" t="s">
+      <c r="D106" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="E106" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="F106" s="59" t="s">
+      <c r="E106" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="F106" s="43" t="s">
         <v>419</v>
       </c>
-      <c r="G106" s="59" t="s">
+      <c r="G106" s="43" t="s">
         <v>597</v>
       </c>
-      <c r="H106" s="59" t="s">
+      <c r="H106" s="43" t="s">
         <v>422</v>
       </c>
-      <c r="I106" s="59" t="s">
+      <c r="I106" s="43" t="s">
         <v>723</v>
       </c>
-      <c r="J106" s="59" t="s">
+      <c r="J106" s="43" t="s">
         <v>726</v>
       </c>
-      <c r="K106" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="L106" s="59" t="s">
+      <c r="K106" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L106" s="43" t="s">
         <v>42</v>
       </c>
       <c r="M106" s="43" t="s">
@@ -11190,7 +11170,7 @@
     <row r="107" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B107" s="10"/>
       <c r="C107" s="25"/>
-      <c r="D107" s="58" t="s">
+      <c r="D107" s="41" t="s">
         <v>42</v>
       </c>
       <c r="E107" s="41" t="s">
@@ -11242,7 +11222,7 @@
     </row>
     <row r="108" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B108" s="14"/>
-      <c r="D108" s="59" t="s">
+      <c r="D108" s="43" t="s">
         <v>42</v>
       </c>
       <c r="E108" s="43" t="s">
@@ -11297,7 +11277,7 @@
         <f>B105+1</f>
         <v>27</v>
       </c>
-      <c r="D109" s="57" t="s">
+      <c r="D109" s="44" t="s">
         <v>52</v>
       </c>
       <c r="E109" s="44" t="s">
@@ -11349,7 +11329,7 @@
     </row>
     <row r="110" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B110" s="16"/>
-      <c r="D110" s="59" t="s">
+      <c r="D110" s="43" t="s">
         <v>42</v>
       </c>
       <c r="E110" s="43" t="s">

--- a/output7/【河洛文讀注音-雅俗通】《心經》.xlsx
+++ b/output7/【河洛文讀注音-雅俗通】《心經》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57383CCE-2041-4948-A667-A44E8A0EF046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F617347E-CFE7-4A4D-8F10-74E59477BE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView minimized="1" xWindow="465" yWindow="3975" windowWidth="28800" windowHeight="11295" tabRatio="718" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10424" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10424" uniqueCount="737">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -679,9 +679,6 @@
     <t>恐</t>
   </si>
   <si>
-    <t>(5, 6)</t>
-  </si>
-  <si>
     <t>(13, 5)</t>
   </si>
   <si>
@@ -868,10 +865,6 @@
   </si>
   <si>
     <t>方音符號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tan-Uan-Jin-Tiong-Kiu2.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1562,12 +1555,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sim1</t>
-  </si>
-  <si>
-    <t>king1</t>
-  </si>
-  <si>
     <t>zu7</t>
   </si>
   <si>
@@ -1779,28 +1766,6 @@
     <t>(13, 16)</t>
   </si>
   <si>
-    <t>sia2</t>
-  </si>
-  <si>
-    <t>sia2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>迦二時</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zi2</t>
-  </si>
-  <si>
-    <t>zi2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>居二曾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>i7</t>
   </si>
   <si>
@@ -2231,9 +2196,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(5, 5); (65, 7)</t>
-  </si>
-  <si>
     <t>(65, 9); (65, 13)</t>
   </si>
   <si>
@@ -2275,17 +2237,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bang7</t>
-  </si>
-  <si>
-    <t>bang7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>江七門</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>kiu3</t>
   </si>
   <si>
@@ -2650,6 +2601,65 @@
   </si>
   <si>
     <t>右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sim1-King1.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zu2</t>
+  </si>
+  <si>
+    <t>zu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍二曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sia3</t>
+  </si>
+  <si>
+    <t>sia3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迦三時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to2</t>
+  </si>
+  <si>
+    <t>to2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高二地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bong7</t>
+  </si>
+  <si>
+    <t>bong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公七門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liap4</t>
+  </si>
+  <si>
+    <t>liap4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼四柳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3041,7 +3051,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3212,6 +3222,17 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="2" borderId="3" xfId="5" applyNumberFormat="1" applyFill="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -3646,7 +3667,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -3654,7 +3675,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="2:11">
@@ -3662,7 +3683,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>217</v>
+        <v>721</v>
       </c>
       <c r="D7" s="36"/>
       <c r="E7" s="36"/>
@@ -3750,7 +3771,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30">
@@ -3758,7 +3779,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30">
@@ -3766,7 +3787,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="30">
@@ -3810,21 +3831,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" t="s">
         <v>182</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>183</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>184</v>
-      </c>
-      <c r="D1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -3833,12 +3854,12 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -3847,7 +3868,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -3863,72 +3884,72 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" t="s">
         <v>182</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>183</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>184</v>
-      </c>
-      <c r="D1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B2" t="s">
-        <v>414</v>
+        <v>728</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B3" t="s">
-        <v>415</v>
+        <v>734</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>627</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B5" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3936,368 +3957,368 @@
         <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B7" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B8" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B9" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B10" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B11" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B12" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B13" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B14" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B15" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B16" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B19" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B21" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B27" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C28" t="s">
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s">
-        <v>475</v>
+        <v>725</v>
       </c>
       <c r="C29" t="s">
         <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C30" t="s">
         <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s">
-        <v>478</v>
+        <v>722</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s">
         <v>30</v>
@@ -4306,7 +4327,7 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -4320,40 +4341,40 @@
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C34" t="s">
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B35" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s">
         <v>111</v>
@@ -4362,245 +4383,245 @@
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B37" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B39" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B40" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B41" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C41" t="s">
         <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B42" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B45" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B46" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C46" t="s">
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C47" t="s">
         <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C48" t="s">
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B49" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B50" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B51" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B52" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B53" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -4614,99 +4635,99 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B55" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B57" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B58" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C58" t="s">
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B59" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B60" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B61" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
@@ -4717,86 +4738,86 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B62" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C62" t="s">
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B63" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="C63" t="s">
         <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B64" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="C64" t="s">
         <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B65" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="C65" t="s">
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B66" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="C66" t="s">
         <v>18</v>
       </c>
       <c r="D66" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B67" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="C67" t="s">
         <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -4810,189 +4831,189 @@
         <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B69" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="C69" t="s">
         <v>18</v>
       </c>
       <c r="D69" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B70" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="C70" t="s">
         <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B71" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C71" t="s">
         <v>18</v>
       </c>
       <c r="D71" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B72" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="C72" t="s">
         <v>18</v>
       </c>
       <c r="D72" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B73" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C73" t="s">
         <v>18</v>
       </c>
       <c r="D73" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B74" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C74" t="s">
         <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B75" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="C75" t="s">
         <v>18</v>
       </c>
       <c r="D75" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B76" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="C76" t="s">
         <v>18</v>
       </c>
       <c r="D76" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B77" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
       </c>
       <c r="D77" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B78" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="C78" t="s">
         <v>18</v>
       </c>
       <c r="D78" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B79" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
       </c>
       <c r="D79" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B80" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="C80" t="s">
         <v>18</v>
       </c>
       <c r="D80" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B81" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="C81" t="s">
         <v>18</v>
       </c>
       <c r="D81" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -5006,7 +5027,7 @@
         <v>18</v>
       </c>
       <c r="D82" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -5014,223 +5035,223 @@
         <v>160</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
         <v>18</v>
       </c>
       <c r="D83" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B84" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="C84" t="s">
         <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B85" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="C85" t="s">
         <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B86" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C86" t="s">
         <v>18</v>
       </c>
       <c r="D86" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B87" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="C87" t="s">
         <v>18</v>
       </c>
       <c r="D87" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B88" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B89" t="s">
-        <v>620</v>
+        <v>731</v>
       </c>
       <c r="C89" t="s">
         <v>18</v>
       </c>
       <c r="D89" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B90" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="C90" t="s">
         <v>18</v>
       </c>
       <c r="D90" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B91" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="C91" t="s">
         <v>18</v>
       </c>
       <c r="D91" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B92" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
       </c>
       <c r="D92" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B93" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="C93" t="s">
         <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B94" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="C94" t="s">
         <v>18</v>
       </c>
       <c r="D94" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B95" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="C95" t="s">
         <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B96" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="C96" t="s">
         <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B97" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="C97" t="s">
         <v>18</v>
       </c>
       <c r="D97" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B98" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="C98" t="s">
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -5244,245 +5265,245 @@
         <v>18</v>
       </c>
       <c r="D99" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B100" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B101" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="C101" t="s">
         <v>18</v>
       </c>
       <c r="D101" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B102" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="C102" t="s">
         <v>18</v>
       </c>
       <c r="D102" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B103" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C103" t="s">
         <v>18</v>
       </c>
       <c r="D103" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B104" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="C104" t="s">
         <v>18</v>
       </c>
       <c r="D104" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B105" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="C105" t="s">
         <v>18</v>
       </c>
       <c r="D105" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B106" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="C106" t="s">
         <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B107" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="C107" t="s">
         <v>18</v>
       </c>
       <c r="D107" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B108" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="C108" t="s">
         <v>18</v>
       </c>
       <c r="D108" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B109" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="C109" t="s">
         <v>18</v>
       </c>
       <c r="D109" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B110" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="C110" t="s">
         <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B111" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="C111" t="s">
         <v>18</v>
       </c>
       <c r="D111" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B112" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="C112" t="s">
         <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B113" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="C113" t="s">
         <v>18</v>
       </c>
       <c r="D113" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B114" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C114" t="s">
         <v>18</v>
       </c>
       <c r="D114" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B115" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="C115" t="s">
         <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B116" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="C116" t="s">
         <v>18</v>
       </c>
       <c r="D116" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
@@ -5498,16 +5519,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" t="s">
         <v>182</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>183</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>184</v>
-      </c>
-      <c r="D1" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -5682,7 +5703,7 @@
       </c>
       <c r="T3" s="13"/>
       <c r="V3" s="54" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
@@ -5908,13 +5929,13 @@
         <v>69</v>
       </c>
       <c r="F8" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="H8" s="43" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="I8" s="43" t="s">
         <v>42</v>
@@ -5923,25 +5944,25 @@
         <v>21</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="L8" s="43" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="M8" s="43" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="N8" s="43" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="O8" s="43" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="P8" s="43" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="Q8" s="43" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="R8" s="43" t="s">
         <v>29</v>
@@ -5966,10 +5987,10 @@
         <v>159</v>
       </c>
       <c r="G9" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="H9" s="44" t="s">
         <v>223</v>
-      </c>
-      <c r="H9" s="44" t="s">
-        <v>225</v>
       </c>
       <c r="I9" s="44" t="s">
         <v>46</v>
@@ -5978,25 +5999,25 @@
         <v>73</v>
       </c>
       <c r="K9" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="L9" s="44" t="s">
         <v>228</v>
       </c>
-      <c r="L9" s="44" t="s">
+      <c r="M9" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="M9" s="44" t="s">
+      <c r="N9" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="N9" s="44" t="s">
+      <c r="O9" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="O9" s="44" t="s">
+      <c r="P9" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="P9" s="44" t="s">
+      <c r="Q9" s="44" t="s">
         <v>238</v>
-      </c>
-      <c r="Q9" s="44" t="s">
-        <v>240</v>
       </c>
       <c r="R9" s="44" t="s">
         <v>58</v>
@@ -6016,13 +6037,13 @@
         <v>123</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="H10" s="43" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I10" s="43" t="s">
         <v>42</v>
@@ -6031,25 +6052,25 @@
         <v>126</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="L10" s="43" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="M10" s="43" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="N10" s="43" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="O10" s="43" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="P10" s="43" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="Q10" s="43" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="R10" s="43" t="s">
         <v>145</v>
@@ -6118,22 +6139,22 @@
         <v>42</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F12" s="43" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="G12" s="43" t="s">
         <v>113</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="I12" s="43" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="J12" s="43" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K12" s="43" t="s">
         <v>42</v>
@@ -6142,16 +6163,16 @@
         <v>71</v>
       </c>
       <c r="M12" s="43" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="N12" s="43" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="O12" s="43" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="P12" s="43" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="Q12" s="43" t="s">
         <v>42</v>
@@ -6173,40 +6194,40 @@
         <v>46</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F13" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="G13" s="44" t="s">
         <v>242</v>
       </c>
-      <c r="G13" s="44" t="s">
+      <c r="H13" s="44" t="s">
         <v>244</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="I13" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="J13" s="44" t="s">
         <v>248</v>
-      </c>
-      <c r="J13" s="44" t="s">
-        <v>250</v>
       </c>
       <c r="K13" s="44" t="s">
         <v>46</v>
       </c>
       <c r="L13" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="M13" s="44" t="s">
         <v>252</v>
       </c>
-      <c r="M13" s="44" t="s">
+      <c r="N13" s="44" t="s">
         <v>254</v>
       </c>
-      <c r="N13" s="44" t="s">
+      <c r="O13" s="44" t="s">
         <v>256</v>
       </c>
-      <c r="O13" s="44" t="s">
+      <c r="P13" s="44" t="s">
         <v>258</v>
-      </c>
-      <c r="P13" s="44" t="s">
-        <v>260</v>
       </c>
       <c r="Q13" s="44" t="s">
         <v>48</v>
@@ -6227,22 +6248,22 @@
         <v>42</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F14" s="43" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>148</v>
       </c>
       <c r="H14" s="43" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="I14" s="43" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="J14" s="43" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K14" s="43" t="s">
         <v>42</v>
@@ -6251,16 +6272,16 @@
         <v>119</v>
       </c>
       <c r="M14" s="43" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="N14" s="43" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="O14" s="43" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="P14" s="43" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="Q14" s="43" t="s">
         <v>42</v>
@@ -6329,13 +6350,13 @@
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="14"/>
       <c r="D16" s="43" t="s">
-        <v>476</v>
+        <v>726</v>
       </c>
       <c r="E16" s="43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F16" s="43" t="s">
-        <v>479</v>
+        <v>723</v>
       </c>
       <c r="G16" s="43" t="s">
         <v>42</v>
@@ -6347,22 +6368,22 @@
         <v>23</v>
       </c>
       <c r="J16" s="43" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="L16" s="43" t="s">
         <v>42</v>
       </c>
       <c r="M16" s="43" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="N16" s="43" t="s">
         <v>23</v>
       </c>
       <c r="O16" s="43" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="P16" s="43" t="s">
         <v>53</v>
@@ -6384,10 +6405,10 @@
         <v>4</v>
       </c>
       <c r="D17" s="44" t="s">
+        <v>260</v>
+      </c>
+      <c r="E17" s="44" t="s">
         <v>262</v>
-      </c>
-      <c r="E17" s="44" t="s">
-        <v>264</v>
       </c>
       <c r="F17" s="44" t="s">
         <v>51</v>
@@ -6396,37 +6417,37 @@
         <v>81</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I17" s="44" t="s">
         <v>45</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="L17" s="44" t="s">
         <v>46</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N17" s="44" t="s">
         <v>45</v>
       </c>
       <c r="O17" s="44" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P17" s="44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q17" s="44" t="s">
         <v>46</v>
       </c>
       <c r="R17" s="44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="S17" s="47" t="s">
         <v>42</v>
@@ -6436,13 +6457,13 @@
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="16"/>
       <c r="D18" s="43" t="s">
-        <v>477</v>
+        <v>727</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>480</v>
+        <v>724</v>
       </c>
       <c r="G18" s="43" t="s">
         <v>42</v>
@@ -6454,22 +6475,22 @@
         <v>122</v>
       </c>
       <c r="J18" s="43" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="K18" s="43" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="L18" s="43" t="s">
         <v>42</v>
       </c>
       <c r="M18" s="43" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="N18" s="43" t="s">
         <v>122</v>
       </c>
       <c r="O18" s="43" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="P18" s="43" t="s">
         <v>140</v>
@@ -6541,22 +6562,22 @@
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="14"/>
       <c r="D20" s="43" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="E20" s="43" t="s">
         <v>65</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G20" s="43" t="s">
         <v>42</v>
       </c>
       <c r="H20" s="43" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="I20" s="43" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="J20" s="43" t="s">
         <v>65</v>
@@ -6577,7 +6598,7 @@
         <v>21</v>
       </c>
       <c r="P20" s="43" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="Q20" s="43" t="s">
         <v>42</v>
@@ -6596,43 +6617,43 @@
         <v>5</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E21" s="44" t="s">
         <v>49</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G21" s="44" t="s">
         <v>46</v>
       </c>
       <c r="H21" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I21" s="44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J21" s="44" t="s">
         <v>49</v>
       </c>
       <c r="K21" s="44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="L21" s="44" t="s">
         <v>46</v>
       </c>
       <c r="M21" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="N21" s="44" t="s">
         <v>273</v>
-      </c>
-      <c r="N21" s="44" t="s">
-        <v>275</v>
       </c>
       <c r="O21" s="44" t="s">
         <v>73</v>
       </c>
       <c r="P21" s="44" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Q21" s="44" t="s">
         <v>46</v>
@@ -6648,22 +6669,22 @@
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="16"/>
       <c r="D22" s="43" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="E22" s="43" t="s">
         <v>151</v>
       </c>
       <c r="F22" s="43" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G22" s="43" t="s">
         <v>42</v>
       </c>
       <c r="H22" s="43" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="I22" s="43" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="J22" s="43" t="s">
         <v>151</v>
@@ -6678,7 +6699,7 @@
         <v>146</v>
       </c>
       <c r="N22" s="43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O22" s="43" t="s">
         <v>126</v>
@@ -6753,10 +6774,10 @@
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="14"/>
       <c r="D24" s="43" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="F24" s="43" t="s">
         <v>65</v>
@@ -6808,10 +6829,10 @@
         <v>6</v>
       </c>
       <c r="D25" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="E25" s="44" t="s">
         <v>280</v>
-      </c>
-      <c r="E25" s="44" t="s">
-        <v>282</v>
       </c>
       <c r="F25" s="44" t="s">
         <v>49</v>
@@ -6862,10 +6883,10 @@
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="16"/>
       <c r="D26" s="43" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="F26" s="43" t="s">
         <v>151</v>
@@ -6914,13 +6935,13 @@
     <row r="27" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B27" s="10"/>
       <c r="C27" s="25"/>
-      <c r="D27" s="41" t="s">
+      <c r="D27" s="58" t="s">
         <v>42</v>
       </c>
       <c r="E27" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="41" t="s">
+      <c r="F27" s="58" t="s">
         <v>42</v>
       </c>
       <c r="G27" s="41" t="s">
@@ -6966,14 +6987,14 @@
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="14"/>
-      <c r="D28" s="43" t="s">
-        <v>476</v>
+      <c r="D28" s="59" t="s">
+        <v>726</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>211</v>
-      </c>
-      <c r="F28" s="43" t="s">
-        <v>479</v>
+        <v>210</v>
+      </c>
+      <c r="F28" s="59" t="s">
+        <v>723</v>
       </c>
       <c r="G28" s="43" t="s">
         <v>42</v>
@@ -6982,13 +7003,13 @@
         <v>65</v>
       </c>
       <c r="I28" s="43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J28" s="43" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="K28" s="43" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="L28" s="43" t="s">
         <v>70</v>
@@ -7006,7 +7027,7 @@
         <v>23</v>
       </c>
       <c r="Q28" s="43" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="R28" s="43" t="s">
         <v>42</v>
@@ -7022,13 +7043,13 @@
         <f>B25+1</f>
         <v>7</v>
       </c>
-      <c r="D29" s="44" t="s">
+      <c r="D29" s="57" t="s">
+        <v>260</v>
+      </c>
+      <c r="E29" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="E29" s="44" t="s">
-        <v>264</v>
-      </c>
-      <c r="F29" s="44" t="s">
+      <c r="F29" s="57" t="s">
         <v>51</v>
       </c>
       <c r="G29" s="44" t="s">
@@ -7038,13 +7059,13 @@
         <v>49</v>
       </c>
       <c r="I29" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="J29" s="44" t="s">
         <v>284</v>
       </c>
-      <c r="J29" s="44" t="s">
-        <v>286</v>
-      </c>
       <c r="K29" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="L29" s="44" t="s">
         <v>61</v>
@@ -7062,7 +7083,7 @@
         <v>45</v>
       </c>
       <c r="Q29" s="44" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="R29" s="44" t="s">
         <v>46</v>
@@ -7075,14 +7096,14 @@
     </row>
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="16"/>
-      <c r="D30" s="43" t="s">
-        <v>477</v>
+      <c r="D30" s="59" t="s">
+        <v>727</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="F30" s="43" t="s">
-        <v>480</v>
+        <v>211</v>
+      </c>
+      <c r="F30" s="59" t="s">
+        <v>724</v>
       </c>
       <c r="G30" s="43" t="s">
         <v>42</v>
@@ -7091,13 +7112,13 @@
         <v>151</v>
       </c>
       <c r="I30" s="43" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J30" s="43" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="K30" s="43" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="L30" s="43" t="s">
         <v>142</v>
@@ -7115,7 +7136,7 @@
         <v>122</v>
       </c>
       <c r="Q30" s="43" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="R30" s="43" t="s">
         <v>42</v>
@@ -7185,13 +7206,13 @@
         <v>23</v>
       </c>
       <c r="E32" s="43" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F32" s="43" t="s">
         <v>23</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="H32" s="43" t="s">
         <v>42</v>
@@ -7206,7 +7227,7 @@
         <v>23</v>
       </c>
       <c r="L32" s="43" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="M32" s="43" t="s">
         <v>42</v>
@@ -7215,13 +7236,13 @@
         <v>65</v>
       </c>
       <c r="O32" s="43" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="P32" s="43" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="Q32" s="43" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="R32" s="43" t="s">
         <v>22</v>
@@ -7241,13 +7262,13 @@
         <v>45</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F33" s="44" t="s">
         <v>45</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H33" s="44" t="s">
         <v>46</v>
@@ -7256,13 +7277,13 @@
         <v>45</v>
       </c>
       <c r="J33" s="44" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="K33" s="44" t="s">
         <v>45</v>
       </c>
       <c r="L33" s="44" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M33" s="44" t="s">
         <v>48</v>
@@ -7271,13 +7292,13 @@
         <v>49</v>
       </c>
       <c r="O33" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="P33" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q33" s="44" t="s">
         <v>300</v>
-      </c>
-      <c r="P33" s="44" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q33" s="44" t="s">
-        <v>302</v>
       </c>
       <c r="R33" s="44" t="s">
         <v>50</v>
@@ -7293,13 +7314,13 @@
         <v>122</v>
       </c>
       <c r="E34" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F34" s="43" t="s">
         <v>122</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="H34" s="43" t="s">
         <v>42</v>
@@ -7314,7 +7335,7 @@
         <v>122</v>
       </c>
       <c r="L34" s="43" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="M34" s="43" t="s">
         <v>42</v>
@@ -7323,13 +7344,13 @@
         <v>151</v>
       </c>
       <c r="O34" s="43" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="P34" s="43" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="Q34" s="43" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="R34" s="43" t="s">
         <v>121</v>
@@ -7413,7 +7434,7 @@
         <v>21</v>
       </c>
       <c r="J36" s="43" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="K36" s="43" t="s">
         <v>42</v>
@@ -7422,22 +7443,22 @@
         <v>22</v>
       </c>
       <c r="M36" s="43" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="N36" s="43" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O36" s="43" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="P36" s="43" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="Q36" s="43" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="R36" s="43" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="S36" s="46" t="s">
         <v>42</v>
@@ -7450,7 +7471,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E37" s="44" t="s">
         <v>46</v>
@@ -7459,16 +7480,16 @@
         <v>50</v>
       </c>
       <c r="G37" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="H37" s="44" t="s">
         <v>273</v>
-      </c>
-      <c r="H37" s="44" t="s">
-        <v>275</v>
       </c>
       <c r="I37" s="44" t="s">
         <v>73</v>
       </c>
       <c r="J37" s="44" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K37" s="44" t="s">
         <v>48</v>
@@ -7477,22 +7498,22 @@
         <v>50</v>
       </c>
       <c r="M37" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="N37" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="N37" s="44" t="s">
+      <c r="O37" s="44" t="s">
         <v>306</v>
       </c>
-      <c r="O37" s="44" t="s">
+      <c r="P37" s="44" t="s">
         <v>308</v>
       </c>
-      <c r="P37" s="44" t="s">
+      <c r="Q37" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="Q37" s="44" t="s">
+      <c r="R37" s="44" t="s">
         <v>312</v>
-      </c>
-      <c r="R37" s="44" t="s">
-        <v>314</v>
       </c>
       <c r="S37" s="47" t="s">
         <v>42</v>
@@ -7514,7 +7535,7 @@
         <v>146</v>
       </c>
       <c r="H38" s="43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I38" s="43" t="s">
         <v>126</v>
@@ -7529,22 +7550,22 @@
         <v>121</v>
       </c>
       <c r="M38" s="43" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="N38" s="43" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O38" s="43" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="P38" s="43" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="Q38" s="43" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="R38" s="43" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="S38" s="49" t="s">
         <v>42</v>
@@ -7625,10 +7646,10 @@
         <v>79</v>
       </c>
       <c r="J40" s="43" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="K40" s="43" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="L40" s="43" t="s">
         <v>42</v>
@@ -7668,22 +7689,22 @@
         <v>50</v>
       </c>
       <c r="F41" s="44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G41" s="44" t="s">
+        <v>314</v>
+      </c>
+      <c r="H41" s="44" t="s">
         <v>316</v>
       </c>
-      <c r="H41" s="44" t="s">
+      <c r="I41" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="I41" s="44" t="s">
+      <c r="J41" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="J41" s="44" t="s">
-        <v>322</v>
-      </c>
       <c r="K41" s="44" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L41" s="44" t="s">
         <v>48</v>
@@ -7734,10 +7755,10 @@
         <v>130</v>
       </c>
       <c r="J42" s="43" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="K42" s="43" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="L42" s="43" t="s">
         <v>42</v>
@@ -7824,10 +7845,10 @@
         <v>22</v>
       </c>
       <c r="E44" s="43" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="F44" s="43" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="G44" s="43" t="s">
         <v>42</v>
@@ -7836,19 +7857,19 @@
         <v>77</v>
       </c>
       <c r="I44" s="43" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="J44" s="43" t="s">
         <v>22</v>
       </c>
       <c r="K44" s="43" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="L44" s="43" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="M44" s="43" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="N44" s="43" t="s">
         <v>42</v>
@@ -7879,10 +7900,10 @@
         <v>50</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F45" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G45" s="44" t="s">
         <v>46</v>
@@ -7891,19 +7912,19 @@
         <v>74</v>
       </c>
       <c r="I45" s="44" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J45" s="44" t="s">
         <v>50</v>
       </c>
       <c r="K45" s="44" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="L45" s="44" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M45" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="N45" s="44" t="s">
         <v>48</v>
@@ -7931,10 +7952,10 @@
         <v>121</v>
       </c>
       <c r="E46" s="43" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="F46" s="43" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="G46" s="43" t="s">
         <v>42</v>
@@ -7943,19 +7964,19 @@
         <v>137</v>
       </c>
       <c r="I46" s="43" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="J46" s="43" t="s">
         <v>121</v>
       </c>
       <c r="K46" s="43" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="L46" s="43" t="s">
         <v>153</v>
       </c>
       <c r="M46" s="43" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="N46" s="43" t="s">
         <v>42</v>
@@ -8045,7 +8066,7 @@
         <v>28</v>
       </c>
       <c r="H48" s="43" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="I48" s="43" t="s">
         <v>42</v>
@@ -8054,7 +8075,7 @@
         <v>77</v>
       </c>
       <c r="K48" s="43" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="L48" s="43" t="s">
         <v>22</v>
@@ -8109,7 +8130,7 @@
         <v>74</v>
       </c>
       <c r="K49" s="44" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L49" s="44" t="s">
         <v>50</v>
@@ -8118,7 +8139,7 @@
         <v>90</v>
       </c>
       <c r="N49" s="44" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O49" s="44" t="s">
         <v>46</v>
@@ -8152,7 +8173,7 @@
         <v>120</v>
       </c>
       <c r="H50" s="43" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="I50" s="43" t="s">
         <v>42</v>
@@ -8161,7 +8182,7 @@
         <v>137</v>
       </c>
       <c r="K50" s="43" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="L50" s="43" t="s">
         <v>121</v>
@@ -8170,7 +8191,7 @@
         <v>144</v>
       </c>
       <c r="N50" s="43" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="O50" s="43" t="s">
         <v>42</v>
@@ -8248,7 +8269,7 @@
         <v>41</v>
       </c>
       <c r="E52" s="43" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="F52" s="43" t="s">
         <v>42</v>
@@ -8300,7 +8321,7 @@
         <v>13</v>
       </c>
       <c r="D53" s="44" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E53" s="44" t="s">
         <v>56</v>
@@ -8354,10 +8375,10 @@
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="16"/>
       <c r="D54" s="43" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="E54" s="43" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="F54" s="43" t="s">
         <v>42</v>
@@ -8462,16 +8483,16 @@
         <v>22</v>
       </c>
       <c r="E56" s="43" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F56" s="43" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="G56" s="43" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="H56" s="43" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="I56" s="43" t="s">
         <v>42</v>
@@ -8517,16 +8538,16 @@
         <v>50</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F57" s="44" t="s">
+        <v>331</v>
+      </c>
+      <c r="G57" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="H57" s="44" t="s">
         <v>333</v>
-      </c>
-      <c r="G57" s="44" t="s">
-        <v>290</v>
-      </c>
-      <c r="H57" s="44" t="s">
-        <v>335</v>
       </c>
       <c r="I57" s="44" t="s">
         <v>48</v>
@@ -8535,7 +8556,7 @@
         <v>50</v>
       </c>
       <c r="K57" s="44" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="L57" s="44" t="s">
         <v>46</v>
@@ -8569,16 +8590,16 @@
         <v>121</v>
       </c>
       <c r="E58" s="43" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F58" s="43" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="G58" s="43" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="H58" s="43" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="I58" s="43" t="s">
         <v>42</v>
@@ -8636,10 +8657,10 @@
       <c r="I59" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="J59" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="K59" s="41" t="s">
+      <c r="J59" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="K59" s="58" t="s">
         <v>42</v>
       </c>
       <c r="L59" s="41" t="s">
@@ -8671,28 +8692,28 @@
     <row r="60" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="14"/>
       <c r="D60" s="43" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="E60" s="43" t="s">
         <v>19</v>
       </c>
       <c r="F60" s="43" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="G60" s="43" t="s">
         <v>42</v>
       </c>
       <c r="H60" s="43" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="I60" s="43" t="s">
-        <v>596</v>
-      </c>
-      <c r="J60" s="43" t="s">
-        <v>421</v>
-      </c>
-      <c r="K60" s="43" t="s">
-        <v>42</v>
+        <v>586</v>
+      </c>
+      <c r="J60" s="59" t="s">
+        <v>417</v>
+      </c>
+      <c r="K60" s="59" t="s">
+        <v>729</v>
       </c>
       <c r="L60" s="43" t="s">
         <v>42</v>
@@ -8701,19 +8722,19 @@
         <v>76</v>
       </c>
       <c r="N60" s="43" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="O60" s="43" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="P60" s="43" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="Q60" s="43" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="R60" s="43" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="S60" s="46" t="s">
         <v>42</v>
@@ -8726,49 +8747,49 @@
         <v>15</v>
       </c>
       <c r="D61" s="44" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E61" s="44" t="s">
         <v>59</v>
       </c>
       <c r="F61" s="44" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G61" s="44" t="s">
         <v>81</v>
       </c>
       <c r="H61" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="I61" s="44" t="s">
+        <v>341</v>
+      </c>
+      <c r="J61" s="57" t="s">
         <v>223</v>
       </c>
-      <c r="I61" s="44" t="s">
+      <c r="K61" s="57" t="s">
         <v>343</v>
-      </c>
-      <c r="J61" s="44" t="s">
-        <v>225</v>
-      </c>
-      <c r="K61" s="44" t="s">
-        <v>345</v>
       </c>
       <c r="L61" s="44" t="s">
         <v>46</v>
       </c>
       <c r="M61" s="44" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N61" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="O61" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="O61" s="44" t="s">
+      <c r="P61" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="P61" s="44" t="s">
+      <c r="Q61" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="Q61" s="44" t="s">
+      <c r="R61" s="44" t="s">
         <v>236</v>
-      </c>
-      <c r="R61" s="44" t="s">
-        <v>238</v>
       </c>
       <c r="S61" s="47" t="s">
         <v>42</v>
@@ -8778,28 +8799,28 @@
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="16"/>
       <c r="D62" s="43" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="E62" s="43" t="s">
         <v>152</v>
       </c>
       <c r="F62" s="43" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G62" s="43" t="s">
         <v>42</v>
       </c>
       <c r="H62" s="43" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="I62" s="43" t="s">
-        <v>597</v>
-      </c>
-      <c r="J62" s="43" t="s">
-        <v>422</v>
-      </c>
-      <c r="K62" s="43" t="s">
-        <v>42</v>
+        <v>587</v>
+      </c>
+      <c r="J62" s="59" t="s">
+        <v>418</v>
+      </c>
+      <c r="K62" s="59" t="s">
+        <v>730</v>
       </c>
       <c r="L62" s="43" t="s">
         <v>42</v>
@@ -8808,19 +8829,19 @@
         <v>132</v>
       </c>
       <c r="N62" s="43" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="O62" s="43" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="P62" s="43" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="Q62" s="43" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="R62" s="43" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="S62" s="49" t="s">
         <v>42</v>
@@ -8883,10 +8904,10 @@
     <row r="64" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B64" s="14"/>
       <c r="D64" s="43" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E64" s="43" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="F64" s="43" t="s">
         <v>42</v>
@@ -8898,10 +8919,10 @@
         <v>19</v>
       </c>
       <c r="I64" s="43" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="J64" s="43" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="K64" s="43" t="s">
         <v>42</v>
@@ -8910,13 +8931,13 @@
         <v>22</v>
       </c>
       <c r="M64" s="43" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="N64" s="43" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="O64" s="43" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="P64" s="43" t="s">
         <v>42</v>
@@ -8938,10 +8959,10 @@
         <v>16</v>
       </c>
       <c r="D65" s="44" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F65" s="44" t="s">
         <v>46</v>
@@ -8953,10 +8974,10 @@
         <v>59</v>
       </c>
       <c r="I65" s="44" t="s">
+        <v>347</v>
+      </c>
+      <c r="J65" s="44" t="s">
         <v>349</v>
-      </c>
-      <c r="J65" s="44" t="s">
-        <v>351</v>
       </c>
       <c r="K65" s="44" t="s">
         <v>46</v>
@@ -8965,13 +8986,13 @@
         <v>50</v>
       </c>
       <c r="M65" s="44" t="s">
+        <v>347</v>
+      </c>
+      <c r="N65" s="44" t="s">
         <v>349</v>
       </c>
-      <c r="N65" s="44" t="s">
-        <v>351</v>
-      </c>
       <c r="O65" s="44" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P65" s="44" t="s">
         <v>46</v>
@@ -8990,10 +9011,10 @@
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="16"/>
       <c r="D66" s="43" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E66" s="43" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="F66" s="43" t="s">
         <v>42</v>
@@ -9005,10 +9026,10 @@
         <v>152</v>
       </c>
       <c r="I66" s="43" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="J66" s="43" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="K66" s="43" t="s">
         <v>42</v>
@@ -9017,13 +9038,13 @@
         <v>121</v>
       </c>
       <c r="M66" s="43" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="N66" s="43" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="O66" s="43" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="P66" s="43" t="s">
         <v>42</v>
@@ -9066,7 +9087,7 @@
       <c r="K67" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="L67" s="41" t="s">
+      <c r="L67" s="58" t="s">
         <v>42</v>
       </c>
       <c r="M67" s="41" t="s">
@@ -9081,7 +9102,7 @@
       <c r="P67" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="Q67" s="41" t="s">
+      <c r="Q67" s="58" t="s">
         <v>42</v>
       </c>
       <c r="R67" s="41" t="s">
@@ -9095,10 +9116,10 @@
     <row r="68" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="14"/>
       <c r="D68" s="43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E68" s="43" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="F68" s="43" t="s">
         <v>42</v>
@@ -9107,19 +9128,19 @@
         <v>20</v>
       </c>
       <c r="H68" s="43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I68" s="43" t="s">
         <v>116</v>
       </c>
       <c r="J68" s="43" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="K68" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="L68" s="43" t="s">
-        <v>621</v>
+      <c r="L68" s="59" t="s">
+        <v>732</v>
       </c>
       <c r="M68" s="43" t="s">
         <v>107</v>
@@ -9128,16 +9149,16 @@
         <v>42</v>
       </c>
       <c r="O68" s="43" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="P68" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="Q68" s="43" t="s">
-        <v>42</v>
+      <c r="Q68" s="59" t="s">
+        <v>735</v>
       </c>
       <c r="R68" s="43" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="S68" s="46" t="s">
         <v>42</v>
@@ -9150,10 +9171,10 @@
         <v>17</v>
       </c>
       <c r="D69" s="44" t="s">
+        <v>350</v>
+      </c>
+      <c r="E69" s="44" t="s">
         <v>352</v>
-      </c>
-      <c r="E69" s="44" t="s">
-        <v>354</v>
       </c>
       <c r="F69" s="44" t="s">
         <v>46</v>
@@ -9162,37 +9183,37 @@
         <v>60</v>
       </c>
       <c r="H69" s="44" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I69" s="44" t="s">
+        <v>355</v>
+      </c>
+      <c r="J69" s="44" t="s">
         <v>357</v>
       </c>
-      <c r="J69" s="44" t="s">
-        <v>359</v>
-      </c>
       <c r="K69" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="L69" s="57" t="s">
         <v>360</v>
       </c>
-      <c r="L69" s="44" t="s">
-        <v>362</v>
-      </c>
       <c r="M69" s="44" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N69" s="44" t="s">
         <v>46</v>
       </c>
       <c r="O69" s="44" t="s">
+        <v>362</v>
+      </c>
+      <c r="P69" s="44" t="s">
         <v>364</v>
       </c>
-      <c r="P69" s="44" t="s">
+      <c r="Q69" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="Q69" s="44" t="s">
+      <c r="R69" s="44" t="s">
         <v>368</v>
-      </c>
-      <c r="R69" s="44" t="s">
-        <v>370</v>
       </c>
       <c r="S69" s="47" t="s">
         <v>42</v>
@@ -9202,10 +9223,10 @@
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="16"/>
       <c r="D70" s="43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E70" s="43" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="F70" s="43" t="s">
         <v>42</v>
@@ -9214,37 +9235,37 @@
         <v>131</v>
       </c>
       <c r="H70" s="43" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I70" s="43" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="J70" s="43" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="K70" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="L70" s="43" t="s">
-        <v>622</v>
+      <c r="L70" s="59" t="s">
+        <v>733</v>
       </c>
       <c r="M70" s="43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N70" s="43" t="s">
         <v>42</v>
       </c>
       <c r="O70" s="43" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="P70" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="Q70" s="43" t="s">
-        <v>42</v>
+      <c r="Q70" s="59" t="s">
+        <v>736</v>
       </c>
       <c r="R70" s="43" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="S70" s="49" t="s">
         <v>42</v>
@@ -9527,10 +9548,10 @@
         <v>67</v>
       </c>
       <c r="F76" s="43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G76" s="43" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="H76" s="43" t="s">
         <v>42</v>
@@ -9539,25 +9560,25 @@
         <v>76</v>
       </c>
       <c r="J76" s="43" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="K76" s="43" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="L76" s="43" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="M76" s="43" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="N76" s="43" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="O76" s="43" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="P76" s="43" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="Q76" s="43" t="s">
         <v>42</v>
@@ -9582,37 +9603,37 @@
         <v>75</v>
       </c>
       <c r="F77" s="44" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G77" s="44" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H77" s="44" t="s">
         <v>46</v>
       </c>
       <c r="I77" s="44" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J77" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="K77" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="K77" s="44" t="s">
+      <c r="L77" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="L77" s="44" t="s">
+      <c r="M77" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="M77" s="44" t="s">
+      <c r="N77" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="N77" s="44" t="s">
+      <c r="O77" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="O77" s="44" t="s">
-        <v>240</v>
-      </c>
       <c r="P77" s="44" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q77" s="44" t="s">
         <v>46</v>
@@ -9634,10 +9655,10 @@
         <v>147</v>
       </c>
       <c r="F78" s="43" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G78" s="43" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="H78" s="43" t="s">
         <v>42</v>
@@ -9646,25 +9667,25 @@
         <v>132</v>
       </c>
       <c r="J78" s="43" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="K78" s="43" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="L78" s="43" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="M78" s="43" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="N78" s="43" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="O78" s="43" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="P78" s="43" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="Q78" s="43" t="s">
         <v>42</v>
@@ -9733,31 +9754,31 @@
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="14"/>
       <c r="D80" s="43" t="s">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="E80" s="43" t="s">
         <v>55</v>
       </c>
       <c r="F80" s="43" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="G80" s="43" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="H80" s="43" t="s">
         <v>105</v>
       </c>
       <c r="I80" s="43" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="J80" s="43" t="s">
         <v>105</v>
       </c>
       <c r="K80" s="43" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="L80" s="43" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="M80" s="43" t="s">
         <v>42</v>
@@ -9788,31 +9809,31 @@
         <v>20</v>
       </c>
       <c r="D81" s="44" t="s">
+        <v>374</v>
+      </c>
+      <c r="E81" s="44" t="s">
         <v>376</v>
       </c>
-      <c r="E81" s="44" t="s">
-        <v>378</v>
-      </c>
       <c r="F81" s="44" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G81" s="44" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H81" s="44" t="s">
         <v>88</v>
       </c>
       <c r="I81" s="44" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J81" s="44" t="s">
         <v>88</v>
       </c>
       <c r="K81" s="44" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L81" s="44" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="M81" s="44" t="s">
         <v>81</v>
@@ -9842,31 +9863,31 @@
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="16"/>
       <c r="D82" s="43" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="E82" s="43" t="s">
         <v>135</v>
       </c>
       <c r="F82" s="43" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="G82" s="43" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="H82" s="43" t="s">
         <v>138</v>
       </c>
       <c r="I82" s="43" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="J82" s="43" t="s">
         <v>138</v>
       </c>
       <c r="K82" s="43" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="L82" s="43" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="M82" s="43" t="s">
         <v>42</v>
@@ -9947,28 +9968,28 @@
     <row r="84" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B84" s="14"/>
       <c r="D84" s="43" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="E84" s="43" t="s">
         <v>64</v>
       </c>
       <c r="F84" s="43" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G84" s="43" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="H84" s="43" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I84" s="43" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="J84" s="43" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="K84" s="43" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="L84" s="43" t="s">
         <v>42</v>
@@ -9977,7 +9998,7 @@
         <v>65</v>
       </c>
       <c r="N84" s="43" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="O84" s="43" t="s">
         <v>27</v>
@@ -10002,28 +10023,28 @@
         <v>21</v>
       </c>
       <c r="D85" s="44" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E85" s="44" t="s">
         <v>57</v>
       </c>
       <c r="F85" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="G85" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="G85" s="44" t="s">
+      <c r="H85" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="H85" s="44" t="s">
+      <c r="I85" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="I85" s="44" t="s">
+      <c r="J85" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="J85" s="44" t="s">
+      <c r="K85" s="44" t="s">
         <v>238</v>
-      </c>
-      <c r="K85" s="44" t="s">
-        <v>240</v>
       </c>
       <c r="L85" s="44" t="s">
         <v>46</v>
@@ -10032,13 +10053,13 @@
         <v>49</v>
       </c>
       <c r="N85" s="44" t="s">
+        <v>380</v>
+      </c>
+      <c r="O85" s="44" t="s">
         <v>382</v>
       </c>
-      <c r="O85" s="44" t="s">
+      <c r="P85" s="44" t="s">
         <v>384</v>
-      </c>
-      <c r="P85" s="44" t="s">
-        <v>386</v>
       </c>
       <c r="Q85" s="44" t="s">
         <v>46</v>
@@ -10054,28 +10075,28 @@
     <row r="86" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B86" s="16"/>
       <c r="D86" s="43" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="E86" s="43" t="s">
         <v>128</v>
       </c>
       <c r="F86" s="43" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G86" s="43" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="H86" s="43" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="I86" s="43" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J86" s="43" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K86" s="43" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L86" s="43" t="s">
         <v>42</v>
@@ -10084,13 +10105,13 @@
         <v>151</v>
       </c>
       <c r="N86" s="43" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="O86" s="43" t="s">
         <v>136</v>
       </c>
       <c r="P86" s="43" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="Q86" s="43" t="s">
         <v>42</v>
@@ -10159,7 +10180,7 @@
     <row r="88" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B88" s="14"/>
       <c r="D88" s="43" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="E88" s="43" t="s">
         <v>28</v>
@@ -10192,10 +10213,10 @@
         <v>22</v>
       </c>
       <c r="O88" s="43" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="P88" s="43" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="Q88" s="43" t="s">
         <v>78</v>
@@ -10214,13 +10235,13 @@
         <v>22</v>
       </c>
       <c r="D89" s="44" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E89" s="44" t="s">
         <v>62</v>
       </c>
       <c r="F89" s="44" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G89" s="44" t="s">
         <v>46</v>
@@ -10232,10 +10253,10 @@
         <v>50</v>
       </c>
       <c r="J89" s="44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K89" s="44" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L89" s="44" t="s">
         <v>46</v>
@@ -10247,13 +10268,13 @@
         <v>50</v>
       </c>
       <c r="O89" s="44" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P89" s="44" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Q89" s="44" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="R89" s="44" t="s">
         <v>48</v>
@@ -10266,13 +10287,13 @@
     <row r="90" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B90" s="16"/>
       <c r="D90" s="43" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="E90" s="43" t="s">
         <v>120</v>
       </c>
       <c r="F90" s="43" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="G90" s="43" t="s">
         <v>42</v>
@@ -10284,10 +10305,10 @@
         <v>121</v>
       </c>
       <c r="J90" s="43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K90" s="43" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="L90" s="43" t="s">
         <v>42</v>
@@ -10299,13 +10320,13 @@
         <v>121</v>
       </c>
       <c r="O90" s="43" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="P90" s="43" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="Q90" s="43" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="R90" s="43" t="s">
         <v>42</v>
@@ -10371,25 +10392,25 @@
     <row r="92" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B92" s="14"/>
       <c r="D92" s="43" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="E92" s="43" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="F92" s="43" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G92" s="43" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="H92" s="43" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="I92" s="43" t="s">
         <v>42</v>
       </c>
       <c r="J92" s="43" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="K92" s="43" t="s">
         <v>68</v>
@@ -10426,25 +10447,25 @@
         <v>23</v>
       </c>
       <c r="D93" s="44" t="s">
+        <v>388</v>
+      </c>
+      <c r="E93" s="44" t="s">
         <v>390</v>
       </c>
-      <c r="E93" s="44" t="s">
-        <v>392</v>
-      </c>
       <c r="F93" s="44" t="s">
+        <v>252</v>
+      </c>
+      <c r="G93" s="44" t="s">
         <v>254</v>
       </c>
-      <c r="G93" s="44" t="s">
+      <c r="H93" s="44" t="s">
         <v>256</v>
-      </c>
-      <c r="H93" s="44" t="s">
-        <v>258</v>
       </c>
       <c r="I93" s="44" t="s">
         <v>81</v>
       </c>
       <c r="J93" s="44" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K93" s="44" t="s">
         <v>87</v>
@@ -10453,7 +10474,7 @@
         <v>45</v>
       </c>
       <c r="M93" s="44" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="N93" s="44" t="s">
         <v>81</v>
@@ -10480,25 +10501,25 @@
     <row r="94" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="16"/>
       <c r="D94" s="43" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="E94" s="43" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="F94" s="43" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="G94" s="43" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="H94" s="43" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I94" s="43" t="s">
         <v>42</v>
       </c>
       <c r="J94" s="43" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="K94" s="43" t="s">
         <v>129</v>
@@ -10585,28 +10606,28 @@
     <row r="96" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B96" s="14"/>
       <c r="D96" s="43" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="E96" s="43" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="F96" s="43" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G96" s="43" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="H96" s="43" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I96" s="43" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="J96" s="43" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="K96" s="43" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="L96" s="43" t="s">
         <v>78</v>
@@ -10615,10 +10636,10 @@
         <v>42</v>
       </c>
       <c r="N96" s="43" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O96" s="43" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="P96" s="43" t="s">
         <v>78</v>
@@ -10640,46 +10661,46 @@
         <v>24</v>
       </c>
       <c r="D97" s="44" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F97" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="G97" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="G97" s="44" t="s">
+      <c r="H97" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="H97" s="44" t="s">
+      <c r="I97" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="I97" s="44" t="s">
+      <c r="J97" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="J97" s="44" t="s">
+      <c r="K97" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="K97" s="44" t="s">
-        <v>240</v>
-      </c>
       <c r="L97" s="44" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M97" s="44" t="s">
         <v>46</v>
       </c>
       <c r="N97" s="44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O97" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="P97" s="44" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q97" s="44" t="s">
         <v>399</v>
-      </c>
-      <c r="P97" s="44" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q97" s="44" t="s">
-        <v>401</v>
       </c>
       <c r="R97" s="44" t="s">
         <v>72</v>
@@ -10692,43 +10713,43 @@
     <row r="98" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="16"/>
       <c r="D98" s="43" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="E98" s="43" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="F98" s="43" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G98" s="43" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="H98" s="43" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="I98" s="43" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J98" s="43" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K98" s="43" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L98" s="43" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="M98" s="43" t="s">
         <v>42</v>
       </c>
       <c r="N98" s="43" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="O98" s="43" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="P98" s="43" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="Q98" s="43" t="s">
         <v>149</v>
@@ -10797,7 +10818,7 @@
     <row r="100" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B100" s="14"/>
       <c r="D100" s="43" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="E100" s="43" t="s">
         <v>114</v>
@@ -10806,7 +10827,7 @@
         <v>42</v>
       </c>
       <c r="G100" s="43" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="H100" s="43" t="s">
         <v>114</v>
@@ -10815,13 +10836,13 @@
         <v>42</v>
       </c>
       <c r="J100" s="43" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="K100" s="43" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="L100" s="43" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="M100" s="43" t="s">
         <v>114</v>
@@ -10830,16 +10851,16 @@
         <v>42</v>
       </c>
       <c r="O100" s="43" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="P100" s="43" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="Q100" s="43" t="s">
         <v>103</v>
       </c>
       <c r="R100" s="43" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="S100" s="46" t="s">
         <v>42</v>
@@ -10852,49 +10873,49 @@
         <v>25</v>
       </c>
       <c r="D101" s="44" t="s">
+        <v>401</v>
+      </c>
+      <c r="E101" s="44" t="s">
         <v>403</v>
-      </c>
-      <c r="E101" s="44" t="s">
-        <v>405</v>
       </c>
       <c r="F101" s="44" t="s">
         <v>46</v>
       </c>
       <c r="G101" s="44" t="s">
+        <v>401</v>
+      </c>
+      <c r="H101" s="44" t="s">
         <v>403</v>
-      </c>
-      <c r="H101" s="44" t="s">
-        <v>405</v>
       </c>
       <c r="I101" s="44" t="s">
         <v>46</v>
       </c>
       <c r="J101" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="K101" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="K101" s="44" t="s">
-        <v>236</v>
-      </c>
       <c r="L101" s="44" t="s">
+        <v>401</v>
+      </c>
+      <c r="M101" s="44" t="s">
         <v>403</v>
-      </c>
-      <c r="M101" s="44" t="s">
-        <v>405</v>
       </c>
       <c r="N101" s="44" t="s">
         <v>46</v>
       </c>
       <c r="O101" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="P101" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="P101" s="44" t="s">
-        <v>236</v>
-      </c>
       <c r="Q101" s="44" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R101" s="44" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="S101" s="47" t="s">
         <v>42</v>
@@ -10904,7 +10925,7 @@
     <row r="102" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B102" s="16"/>
       <c r="D102" s="43" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="E102" s="43" t="s">
         <v>154</v>
@@ -10913,7 +10934,7 @@
         <v>42</v>
       </c>
       <c r="G102" s="43" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="H102" s="43" t="s">
         <v>154</v>
@@ -10922,13 +10943,13 @@
         <v>42</v>
       </c>
       <c r="J102" s="43" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="K102" s="43" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="L102" s="43" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="M102" s="43" t="s">
         <v>154</v>
@@ -10937,16 +10958,16 @@
         <v>42</v>
       </c>
       <c r="O102" s="43" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="P102" s="43" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="Q102" s="43" t="s">
         <v>133</v>
       </c>
       <c r="R102" s="43" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="S102" s="49" t="s">
         <v>42</v>
@@ -11015,19 +11036,19 @@
         <v>42</v>
       </c>
       <c r="F104" s="43" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G104" s="43" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="H104" s="43" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="I104" s="43" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="J104" s="43" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
       <c r="K104" s="43" t="s">
         <v>42</v>
@@ -11064,25 +11085,25 @@
         <v>26</v>
       </c>
       <c r="D105" s="44" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E105" s="44" t="s">
         <v>46</v>
       </c>
       <c r="F105" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="G105" s="44" t="s">
+        <v>341</v>
+      </c>
+      <c r="H105" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="G105" s="44" t="s">
-        <v>343</v>
-      </c>
-      <c r="H105" s="44" t="s">
-        <v>225</v>
-      </c>
       <c r="I105" s="44" t="s">
+        <v>407</v>
+      </c>
+      <c r="J105" s="44" t="s">
         <v>409</v>
-      </c>
-      <c r="J105" s="44" t="s">
-        <v>411</v>
       </c>
       <c r="K105" s="44" t="s">
         <v>81</v>
@@ -11124,19 +11145,19 @@
         <v>42</v>
       </c>
       <c r="F106" s="43" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="G106" s="43" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="H106" s="43" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I106" s="43" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="J106" s="43" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="K106" s="43" t="s">
         <v>42</v>

--- a/output7/【河洛文讀注音-雅俗通】《心經》.xlsx
+++ b/output7/【河洛文讀注音-雅俗通】《心經》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F617347E-CFE7-4A4D-8F10-74E59477BE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5878F44F-D664-411F-84D3-543591FDFE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="465" yWindow="3975" windowWidth="28800" windowHeight="11295" tabRatio="718" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -3051,7 +3051,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3222,17 +3222,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="2" borderId="3" xfId="5" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -6935,13 +6924,13 @@
     <row r="27" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B27" s="10"/>
       <c r="C27" s="25"/>
-      <c r="D27" s="58" t="s">
+      <c r="D27" s="41" t="s">
         <v>42</v>
       </c>
       <c r="E27" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="58" t="s">
+      <c r="F27" s="41" t="s">
         <v>42</v>
       </c>
       <c r="G27" s="41" t="s">
@@ -6987,13 +6976,13 @@
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="14"/>
-      <c r="D28" s="59" t="s">
+      <c r="D28" s="43" t="s">
         <v>726</v>
       </c>
       <c r="E28" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="43" t="s">
         <v>723</v>
       </c>
       <c r="G28" s="43" t="s">
@@ -7043,13 +7032,13 @@
         <f>B25+1</f>
         <v>7</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="44" t="s">
         <v>260</v>
       </c>
       <c r="E29" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="44" t="s">
         <v>51</v>
       </c>
       <c r="G29" s="44" t="s">
@@ -7096,13 +7085,13 @@
     </row>
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="16"/>
-      <c r="D30" s="59" t="s">
+      <c r="D30" s="43" t="s">
         <v>727</v>
       </c>
       <c r="E30" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="43" t="s">
         <v>724</v>
       </c>
       <c r="G30" s="43" t="s">
@@ -8657,10 +8646,10 @@
       <c r="I59" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="J59" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="K59" s="58" t="s">
+      <c r="J59" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K59" s="41" t="s">
         <v>42</v>
       </c>
       <c r="L59" s="41" t="s">
@@ -8709,10 +8698,10 @@
       <c r="I60" s="43" t="s">
         <v>586</v>
       </c>
-      <c r="J60" s="59" t="s">
+      <c r="J60" s="43" t="s">
         <v>417</v>
       </c>
-      <c r="K60" s="59" t="s">
+      <c r="K60" s="43" t="s">
         <v>729</v>
       </c>
       <c r="L60" s="43" t="s">
@@ -8764,10 +8753,10 @@
       <c r="I61" s="44" t="s">
         <v>341</v>
       </c>
-      <c r="J61" s="57" t="s">
+      <c r="J61" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="K61" s="57" t="s">
+      <c r="K61" s="44" t="s">
         <v>343</v>
       </c>
       <c r="L61" s="44" t="s">
@@ -8816,10 +8805,10 @@
       <c r="I62" s="43" t="s">
         <v>587</v>
       </c>
-      <c r="J62" s="59" t="s">
+      <c r="J62" s="43" t="s">
         <v>418</v>
       </c>
-      <c r="K62" s="59" t="s">
+      <c r="K62" s="43" t="s">
         <v>730</v>
       </c>
       <c r="L62" s="43" t="s">
@@ -9087,7 +9076,7 @@
       <c r="K67" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="L67" s="58" t="s">
+      <c r="L67" s="41" t="s">
         <v>42</v>
       </c>
       <c r="M67" s="41" t="s">
@@ -9102,7 +9091,7 @@
       <c r="P67" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="Q67" s="58" t="s">
+      <c r="Q67" s="41" t="s">
         <v>42</v>
       </c>
       <c r="R67" s="41" t="s">
@@ -9139,7 +9128,7 @@
       <c r="K68" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="L68" s="59" t="s">
+      <c r="L68" s="43" t="s">
         <v>732</v>
       </c>
       <c r="M68" s="43" t="s">
@@ -9154,7 +9143,7 @@
       <c r="P68" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="Q68" s="59" t="s">
+      <c r="Q68" s="43" t="s">
         <v>735</v>
       </c>
       <c r="R68" s="43" t="s">
@@ -9194,7 +9183,7 @@
       <c r="K69" s="44" t="s">
         <v>358</v>
       </c>
-      <c r="L69" s="57" t="s">
+      <c r="L69" s="44" t="s">
         <v>360</v>
       </c>
       <c r="M69" s="44" t="s">
@@ -9209,7 +9198,7 @@
       <c r="P69" s="44" t="s">
         <v>364</v>
       </c>
-      <c r="Q69" s="57" t="s">
+      <c r="Q69" s="44" t="s">
         <v>366</v>
       </c>
       <c r="R69" s="44" t="s">
@@ -9246,7 +9235,7 @@
       <c r="K70" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="L70" s="59" t="s">
+      <c r="L70" s="43" t="s">
         <v>733</v>
       </c>
       <c r="M70" s="43" t="s">
@@ -9261,7 +9250,7 @@
       <c r="P70" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="Q70" s="59" t="s">
+      <c r="Q70" s="43" t="s">
         <v>736</v>
       </c>
       <c r="R70" s="43" t="s">
